--- a/金融業AI場景應用.xlsx
+++ b/金融業AI場景應用.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\21510\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9778ED6A-4357-466E-8D48-61B57364A861}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84F04E8C-C435-4100-BBB5-D7822910D72B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{211BE5A6-D4CD-4034-B4EA-61E6D2D0F62C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{211BE5A6-D4CD-4034-B4EA-61E6D2D0F62C}"/>
   </bookViews>
   <sheets>
     <sheet name="AI應用場景" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="分類說明" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="類別選項">分類說明!$A$5:$A$17</definedName>
+    <definedName name="類別選項">分類說明!$A$5:$A$18</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="283">
   <si>
     <t>業別</t>
   </si>
@@ -737,9 +737,6 @@
   </si>
   <si>
     <t>原文明確稱為 AI 代理人。</t>
-  </si>
-  <si>
-    <t>本表僅華南銀行；不因名稱含「助理」「機器人」或「AI 投資長」就推定為自主代理。</t>
   </si>
   <si>
     <t>原文明確使用 AI OCR 進行文件或表單辨識及欄位擷取。</t>
@@ -886,10 +883,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>「富邦 AI PRO」：內建 AI 投資助理，即時解析市場訊息並回答投資問題；快速彙整法說會重點；透過 AI 主播每日播報盤前焦點資訊（原文未交代語音合成技術）；並依個人偏好推送個股新聞事件、盤勢摘要與策略資訊。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>聯博投信</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -902,11 +895,27 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>拆分原則：每列為一個可獨立辨識的用途；同一產品若涵蓋不同功能可拆列。同一 Copilot 辦公套件的常見工作則合併敘述，筆數不等於系統數或成熟度。 全盈支付依指定將軟體開發、資料庫語言審查及白箱測試風險修復合併為一筆，歸類為程式助手。 富邦證券依指定將 AI 投資助理的市場問答、美股法說會摘要及每日盤前資訊播報合併為一筆，歸類為生成式AI。 永豐金證券依指定將個股 AI 市場輿情分析及每日投資早報合併為一筆，歸類為生成式AI。 統一期貨依指定將資料整理、簡報生成及複雜文件處理合併為一筆，歸類為 M365 Copilot。 富邦期貨依指定將「富邦 AI PRO」投資問答、法說會摘要、AI 主播盤前播報及個人化資訊推送合併為一筆，歸類為生成式AI。 聯博投信依指定將 ABAI 的文件資料聊天查詢、資料抽取、文件比較、圖表生成、Text-to-SQL 及安全 API 支援合併為一筆，歸類為其它；其餘場景保留。</t>
-  </si>
-  <si>
     <t>員工通用 AI 生產力輔助工具（原文未詳述功能，判斷為M365 Copilot）。</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>App</t>
+  </si>
+  <si>
+    <t>場景描述與 App 有關者歸入此類。</t>
+  </si>
+  <si>
+    <t>目前無場景歸入此類；不因名稱含「助理」「機器人」或「AI 投資長」就推定為自主代理。</t>
+  </si>
+  <si>
+    <t>「富邦 AI PRO App」：內建 AI 投資助理，即時解析市場訊息並回答投資問題；快速彙整法說會重點；透過 AI 主播每日播報盤前焦點資訊（原文未交代語音合成技術）；並依個人偏好推送個股新聞事件、盤勢摘要與策略資訊。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>拆分原則：每列為一個可獨立辨識的用途；同一產品若涵蓋不同功能可拆列。同一 Copilot 辦公套件的常見工作則合併敘述，筆數不等於系統數或成熟度。 全盈支付依指定將軟體開發、資料庫語言審查及白箱測試風險修復合併為一筆，歸類為程式助手。 富邦證券依指定將 AI 投資助理的市場問答、美股法說會摘要及每日盤前資訊播報合併為一筆，歸類為生成式AI。 永豐金證券依指定將個股 AI 市場輿情分析及每日投資早報合併為一筆，歸類為生成式AI。 統一期貨依指定將資料整理、簡報生成及複雜文件處理合併為一筆，歸類為 M365 Copilot。 富邦期貨依指定將「富邦 AI PRO」投資問答、法說會摘要、AI 主播盤前播報及個人化資訊推送合併為一筆，並依使用者指定改歸 App。 聯博投信依指定將 ABAI 的文件資料聊天查詢、資料抽取、文件比較、圖表生成、Text-to-SQL 及安全 API 支援合併為一筆，歸類為其它；其餘場景保留。</t>
+  </si>
+  <si>
+    <t>場景描述只要提及「App」即歸入此類；亦可由使用者手動將場景類別指定為 App，不以描述是否提及「App」為限。</t>
   </si>
 </sst>
 </file>
@@ -1008,7 +1017,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1026,24 +1035,6 @@
     </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
@@ -1066,69 +1057,26 @@
     <xf numFmtId="1" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="11">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF17365D"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF17365D"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1213,6 +1161,18 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF17365D"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -1291,6 +1251,52 @@
       </font>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF17365D"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1309,26 +1315,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1479BAE9-3403-4530-84D1-035142A43395}" name="金融業AI場景明細" displayName="金融業AI場景明細" ref="A1:D135" totalsRowShown="0" headerRowDxfId="2" dataDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1479BAE9-3403-4530-84D1-035142A43395}" name="金融業AI場景明細" displayName="金融業AI場景明細" ref="A1:D135" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
   <autoFilter ref="A1:D135" xr:uid="{1479BAE9-3403-4530-84D1-035142A43395}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{12B14B75-68EB-44D5-A819-75BBF8DDA766}" name="業別" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{17F96BBF-96D4-48BC-AA3B-DA2A99086A2A}" name="業者" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{316A4304-4041-4733-8CF5-A495037B502A}" name="場景" dataDxfId="0"/>
-    <tableColumn id="4" xr3:uid="{C7B07D9D-96D2-4C10-A243-607A71723345}" name="類別" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{12B14B75-68EB-44D5-A819-75BBF8DDA766}" name="業別" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{17F96BBF-96D4-48BC-AA3B-DA2A99086A2A}" name="業者" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{316A4304-4041-4733-8CF5-A495037B502A}" name="場景" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{C7B07D9D-96D2-4C10-A243-607A71723345}" name="類別" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{856BAA9D-97F8-46A5-A531-72752F2DC511}" name="業者來源索引" displayName="業者來源索引" ref="A1:D81" totalsRowShown="0" headerRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{856BAA9D-97F8-46A5-A531-72752F2DC511}" name="業者來源索引" displayName="業者來源索引" ref="A1:D81" totalsRowShown="0" headerRowDxfId="4">
   <autoFilter ref="A1:D81" xr:uid="{856BAA9D-97F8-46A5-A531-72752F2DC511}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{354CEA03-CED4-4777-A7A3-DB73A2BD0BB5}" name="業別" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{FB14F06D-5CB8-45D7-A20C-B74B7AE1A501}" name="業者" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{A303F6B9-B8F9-43D9-B943-D42481E19E05}" name="PDF頁碼" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{BE0A5CA3-332E-48C8-941D-4E6F65548952}" name="場景筆數" dataDxfId="3">
+    <tableColumn id="1" xr3:uid="{354CEA03-CED4-4777-A7A3-DB73A2BD0BB5}" name="業別" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{FB14F06D-5CB8-45D7-A20C-B74B7AE1A501}" name="業者" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{A303F6B9-B8F9-43D9-B943-D42481E19E05}" name="PDF頁碼" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{BE0A5CA3-332E-48C8-941D-4E6F65548952}" name="場景筆數" dataDxfId="0">
       <calculatedColumnFormula>COUNTIFS(AI應用場景!A:A,A2,AI應用場景!B:B,B2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1663,16 +1669,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="14" t="s">
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1799,7 +1805,7 @@
         <v>24</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1813,7 +1819,7 @@
         <v>25</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="30">
@@ -1855,7 +1861,7 @@
         <v>31</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1869,7 +1875,7 @@
         <v>33</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1911,7 +1917,7 @@
         <v>36</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1939,7 +1945,7 @@
         <v>40</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="30">
@@ -1967,7 +1973,7 @@
         <v>44</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1995,7 +2001,7 @@
         <v>48</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2037,7 +2043,7 @@
         <v>54</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2093,7 +2099,7 @@
         <v>60</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2107,7 +2113,7 @@
         <v>61</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2121,7 +2127,7 @@
         <v>62</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2135,7 +2141,7 @@
         <v>63</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2160,7 +2166,7 @@
         <v>65</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>16</v>
@@ -2174,10 +2180,10 @@
         <v>66</v>
       </c>
       <c r="C37" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>260</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2191,7 +2197,7 @@
         <v>68</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2233,7 +2239,7 @@
         <v>73</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2261,7 +2267,7 @@
         <v>75</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2401,7 +2407,7 @@
         <v>89</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2415,7 +2421,7 @@
         <v>91</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2429,7 +2435,7 @@
         <v>218</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2443,7 +2449,7 @@
         <v>93</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2513,7 +2519,7 @@
         <v>99</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2541,7 +2547,7 @@
         <v>102</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="30">
@@ -2597,7 +2603,7 @@
         <v>108</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2737,7 +2743,7 @@
         <v>126</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2751,7 +2757,7 @@
         <v>128</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2776,13 +2782,13 @@
         <v>129</v>
       </c>
       <c r="C80" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D80" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="D80" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" ht="30">
+    </row>
+    <row r="81" spans="1:4" ht="45">
       <c r="A81" s="3" t="s">
         <v>80</v>
       </c>
@@ -2796,7 +2802,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
+    <row r="82" spans="1:4" ht="45">
       <c r="A82" s="3" t="s">
         <v>80</v>
       </c>
@@ -2821,10 +2827,10 @@
         <v>134</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="45">
       <c r="A84" s="3" t="s">
         <v>80</v>
       </c>
@@ -2838,7 +2844,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="85" spans="1:4">
+    <row r="85" spans="1:4" ht="45">
       <c r="A85" s="3" t="s">
         <v>80</v>
       </c>
@@ -2852,7 +2858,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="86" spans="1:4">
+    <row r="86" spans="1:4" ht="45">
       <c r="A86" s="3" t="s">
         <v>80</v>
       </c>
@@ -2866,7 +2872,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="87" spans="1:4">
+    <row r="87" spans="1:4" ht="45">
       <c r="A87" s="3" t="s">
         <v>80</v>
       </c>
@@ -2880,7 +2886,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:4">
+    <row r="88" spans="1:4" ht="45">
       <c r="A88" s="3" t="s">
         <v>80</v>
       </c>
@@ -2894,7 +2900,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="89" spans="1:4">
+    <row r="89" spans="1:4" ht="45">
       <c r="A89" s="3" t="s">
         <v>80</v>
       </c>
@@ -2919,7 +2925,7 @@
         <v>142</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="45">
@@ -2933,10 +2939,10 @@
         <v>143</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="45">
       <c r="A92" s="3" t="s">
         <v>80</v>
       </c>
@@ -2950,7 +2956,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="93" spans="1:4">
+    <row r="93" spans="1:4" ht="45">
       <c r="A93" s="3" t="s">
         <v>80</v>
       </c>
@@ -2975,7 +2981,7 @@
         <v>147</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="45">
@@ -2989,10 +2995,10 @@
         <v>149</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="45">
       <c r="A96" s="3" t="s">
         <v>80</v>
       </c>
@@ -3003,10 +3009,10 @@
         <v>151</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="45">
       <c r="A97" s="3" t="s">
         <v>80</v>
       </c>
@@ -3031,7 +3037,7 @@
         <v>155</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3095,13 +3101,13 @@
         <v>153</v>
       </c>
       <c r="B103" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C103" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="C103" s="3" t="s">
+      <c r="D103" s="3" t="s">
         <v>267</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3126,10 +3132,10 @@
         <v>166</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3213,7 +3219,7 @@
         <v>175</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3252,10 +3258,10 @@
         <v>178</v>
       </c>
       <c r="C114" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="D114" s="3" t="s">
         <v>271</v>
-      </c>
-      <c r="D114" s="3" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="45">
@@ -3263,13 +3269,13 @@
         <v>153</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="30">
@@ -3336,7 +3342,7 @@
         <v>182</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D120" s="3" t="s">
         <v>13</v>
@@ -3389,13 +3395,13 @@
         <v>153</v>
       </c>
       <c r="B124" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="D124" s="3" t="s">
         <v>275</v>
-      </c>
-      <c r="C124" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="D124" s="3" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3535,7 +3541,7 @@
         <v>210</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3577,16 +3583,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="16" t="s">
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="10" t="s">
         <v>214</v>
       </c>
     </row>
@@ -4801,7 +4807,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4077AB08-966E-46CD-ADDA-66ADF60D95BA}">
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="16.625" customWidth="1"/>
@@ -4811,20 +4817,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24.75">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="14" t="s">
         <v>219</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1"/>
@@ -4833,62 +4839,62 @@
       <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="9" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30">
-      <c r="A5" s="17" t="s">
-        <v>270</v>
-      </c>
-      <c r="B5" s="17" t="s">
+      <c r="A5" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="12">
         <f>COUNTIF(AI應用場景!D:D,A5)</f>
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30">
       <c r="A6" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="D6" s="12">
+      <c r="D6" s="6">
         <f>COUNTIF(AI應用場景!D:D,A6)</f>
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="C7" s="17" t="s">
-        <v>246</v>
-      </c>
-      <c r="D7" s="18">
+      <c r="D7" s="12">
         <f>COUNTIF(AI應用場景!D:D,A7)</f>
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -4901,22 +4907,22 @@
       <c r="C8" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="6">
         <f>COUNTIF(AI應用場景!D:D,A8)</f>
         <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="12">
         <f>COUNTIF(AI應用場景!D:D,A9)</f>
         <v>12</v>
       </c>
@@ -4929,24 +4935,24 @@
         <v>229</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="D10" s="12">
+        <v>246</v>
+      </c>
+      <c r="D10" s="6">
         <f>COUNTIF(AI應用場景!D:D,A10)</f>
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="C11" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="D11" s="18">
+      <c r="C11" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="D11" s="12">
         <f>COUNTIF(AI應用場景!D:D,A11)</f>
         <v>0</v>
       </c>
@@ -4956,195 +4962,210 @@
         <v>120</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="D12" s="12">
+      <c r="D12" s="6">
         <f>COUNTIF(AI應用場景!D:D,A12)</f>
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="30">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="17" t="s">
-        <v>234</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>255</v>
-      </c>
-      <c r="D13" s="18">
+      <c r="B13" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="D13" s="12">
         <f>COUNTIF(AI應用場景!D:D,A13)</f>
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="30">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="B14" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="C14" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="C14" s="17" t="s">
-        <v>244</v>
-      </c>
-      <c r="D14" s="18">
+      <c r="D14" s="12">
         <f>COUNTIF(AI應用場景!D:D,A14)</f>
         <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="30">
-      <c r="A15" s="17" t="s">
-        <v>250</v>
-      </c>
-      <c r="B15" s="17" t="s">
+      <c r="A15" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="C15" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="C15" s="17" t="s">
-        <v>257</v>
-      </c>
-      <c r="D15" s="18">
+      <c r="D15" s="12">
         <f>COUNTIF(AI應用場景!D:D,A15)</f>
         <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="30">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="C16" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="C16" s="17" t="s">
-        <v>264</v>
-      </c>
-      <c r="D16" s="18">
+      <c r="D16" s="12">
         <f>COUNTIF(AI應用場景!D:D,A16)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="45">
-      <c r="A17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>235</v>
+    <row r="17" spans="1:4" ht="30">
+      <c r="A17" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>282</v>
       </c>
       <c r="D17" s="12">
         <f>COUNTIF(AI應用場景!D:D,A17)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="45">
+      <c r="A18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D18" s="6">
+        <f>COUNTIF(AI應用場景!D:D,A18)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="8" t="s">
+    <row r="19" spans="1:4">
+      <c r="A19" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="7">
+        <f>SUM(D5:D18)</f>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="13">
-        <f>SUM(D5:D17)</f>
-        <v>134</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="9" t="s">
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="13" t="str">
+        <f>"整理單位：共 80 個業者／周邊單位、"&amp;D19&amp;" 筆場景；保留原文業別及出現順序，不依業者名稱重新推定監理業別。"</f>
+        <v>整理單位：共 80 個業者／周邊單位、134 筆場景；保留原文業別及出現順序，不依業者名稱重新推定監理業別。</v>
+      </c>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+    </row>
+    <row r="23" spans="1:4" ht="189.95" customHeight="1">
+      <c r="A23" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+    </row>
+    <row r="24" spans="1:4" ht="56.1" customHeight="1">
+      <c r="A24" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+    </row>
+    <row r="25" spans="1:4" ht="36" customHeight="1">
+      <c r="A25" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="10" t="str">
-        <f>"整理單位：共 80 個業者／周邊單位、"&amp;D18&amp;" 筆場景；保留原文業別及出現順序，不依業者名稱重新推定監理業別。"</f>
-        <v>整理單位：共 80 個業者／周邊單位、134 筆場景；保留原文業別及出現順序，不依業者名稱重新推定監理業別。</v>
-      </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-    </row>
-    <row r="22" spans="1:4" ht="189.95" customHeight="1">
-      <c r="A22" s="10" t="s">
-        <v>278</v>
-      </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-    </row>
-    <row r="23" spans="1:4" ht="56.1" customHeight="1">
-      <c r="A23" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-    </row>
-    <row r="24" spans="1:4" ht="36" customHeight="1">
-      <c r="A24" s="11" t="s">
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="11" t="s">
-        <v>248</v>
-      </c>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="11" t="s">
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="11" t="s">
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A22:D22"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A22:D22"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/金融業AI場景應用.xlsx
+++ b/金融業AI場景應用.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\21510\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAFF3C05-D130-498E-BFAC-62F81863B0C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E3FBB05-A345-46CB-AEEB-A14286A0D94A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="344">
   <si>
     <t>台灣金融業 AI 應用｜分類說明</t>
   </si>
@@ -1105,12 +1105,19 @@
   </si>
   <si>
     <t>依指定14組名稱關鍵字重新歸類，多項符合時依表列順序優先；未符合者標為「未歸類」，不代表已確認無金控隸屬。結果以分類值保存，可透過主表下拉選單手動調整。</t>
+  </si>
+  <si>
+    <t>更新日期</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
+  </numFmts>
   <fonts count="11">
     <font>
       <sz val="12"/>
@@ -1285,22 +1292,6 @@
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -1316,26 +1307,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1346,17 +1328,90 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="13">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </font>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </font>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </font>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1377,6 +1432,77 @@
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </font>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </font>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </font>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF17365D"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
@@ -1456,109 +1582,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </font>
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </font>
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </font>
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </font>
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </font>
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF17365D"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1577,27 +1600,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="金融業AI場景明細" displayName="金融業AI場景明細" ref="A1:E144" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A1:E144" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="業別" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="業者" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{906D0F41-B96D-4D39-AA8A-4BFFA48C4FAB}" name="所屬金控" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="場景" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="類別" dataDxfId="6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="金融業AI場景明細" displayName="金融業AI場景明細" ref="A1:F144" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+  <autoFilter ref="A1:F144" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="業別" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="業者" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{906D0F41-B96D-4D39-AA8A-4BFFA48C4FAB}" name="所屬金控" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="場景" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="類別" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{CA636ECA-868F-454F-9C02-6021336C3E99}" name="更新日期" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="業者來源索引" displayName="業者來源索引" ref="A1:D83" totalsRowShown="0" headerRowDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="業者來源索引" displayName="業者來源索引" ref="A1:D83" totalsRowShown="0" headerRowDxfId="12">
   <autoFilter ref="A1:D83" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="業別" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="業者" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="PDF頁碼" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="場景筆數" dataDxfId="1">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="業別" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="業者" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="PDF頁碼" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="場景筆數" dataDxfId="8">
       <calculatedColumnFormula>COUNTIFS(AI應用場景!A:A,A2,AI應用場景!B:B,B2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1922,7 +1946,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E144"/>
+  <dimension ref="A1:F144"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.25" style="13" bestFit="1" customWidth="1"/>
@@ -1930,9 +1954,10 @@
     <col min="3" max="3" width="11.25" style="13" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="90" style="13" customWidth="1"/>
     <col min="5" max="5" width="14.125" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="8" t="s">
         <v>57</v>
       </c>
@@ -1948,15 +1973,18 @@
       <c r="E1" s="8" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="8" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="20" t="s">
         <v>325</v>
       </c>
       <c r="D2" s="3" t="s">
@@ -1965,15 +1993,18 @@
       <c r="E2" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="20" t="s">
         <v>325</v>
       </c>
       <c r="D3" s="3" t="s">
@@ -1982,15 +2013,18 @@
       <c r="E3" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="20" t="s">
         <v>325</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -1999,15 +2033,18 @@
       <c r="E4" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="30" customHeight="1">
+      <c r="F4" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="30" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="3" t="s">
         <v>337</v>
       </c>
       <c r="D5" s="3" t="s">
@@ -2016,15 +2053,18 @@
       <c r="E5" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="30" customHeight="1">
+      <c r="F5" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="30" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="20" t="s">
         <v>327</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -2033,15 +2073,18 @@
       <c r="E6" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="C7" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -2050,15 +2093,18 @@
       <c r="E7" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="F7" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -2067,15 +2113,18 @@
       <c r="E8" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="F8" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="20" t="s">
         <v>328</v>
       </c>
       <c r="D9" s="3" t="s">
@@ -2084,15 +2133,18 @@
       <c r="E9" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="F9" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="20" t="s">
         <v>328</v>
       </c>
       <c r="D10" s="3" t="s">
@@ -2101,15 +2153,18 @@
       <c r="E10" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="F10" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="20" t="s">
         <v>328</v>
       </c>
       <c r="D11" s="3" t="s">
@@ -2118,15 +2173,18 @@
       <c r="E11" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" ht="30" customHeight="1">
+      <c r="F11" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="30" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="31" t="s">
+      <c r="C12" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D12" s="3" t="s">
@@ -2135,15 +2193,18 @@
       <c r="E12" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="F12" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="31" t="s">
+      <c r="C13" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D13" s="3" t="s">
@@ -2152,15 +2213,18 @@
       <c r="E13" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="F13" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C14" s="31" t="s">
+      <c r="C14" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -2169,15 +2233,18 @@
       <c r="E14" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="F14" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="C15" s="20" t="s">
         <v>329</v>
       </c>
       <c r="D15" s="3" t="s">
@@ -2186,15 +2253,18 @@
       <c r="E15" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="F15" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="27" t="s">
+      <c r="C16" s="20" t="s">
         <v>329</v>
       </c>
       <c r="D16" s="3" t="s">
@@ -2203,15 +2273,18 @@
       <c r="E16" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="20" t="s">
         <v>329</v>
       </c>
       <c r="D17" s="3" t="s">
@@ -2220,15 +2293,18 @@
       <c r="E17" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C18" s="27" t="s">
+      <c r="C18" s="20" t="s">
         <v>329</v>
       </c>
       <c r="D18" s="3" t="s">
@@ -2237,15 +2313,18 @@
       <c r="E18" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C19" s="27" t="s">
+      <c r="C19" s="20" t="s">
         <v>329</v>
       </c>
       <c r="D19" s="3" t="s">
@@ -2254,15 +2333,18 @@
       <c r="E19" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" ht="30" customHeight="1">
+      <c r="F19" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="30" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C20" s="31" t="s">
+      <c r="C20" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D20" s="3" t="s">
@@ -2271,15 +2353,18 @@
       <c r="E20" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" ht="30" customHeight="1">
+      <c r="F20" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="30" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C21" s="31" t="s">
+      <c r="C21" s="3" t="s">
         <v>337</v>
       </c>
       <c r="D21" s="3" t="s">
@@ -2288,15 +2373,18 @@
       <c r="E21" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" ht="30" customHeight="1">
+      <c r="F21" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="30" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C22" s="27" t="s">
+      <c r="C22" s="20" t="s">
         <v>327</v>
       </c>
       <c r="D22" s="3" t="s">
@@ -2305,15 +2393,18 @@
       <c r="E22" s="3" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="F22" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="27" t="s">
+      <c r="C23" s="20" t="s">
         <v>330</v>
       </c>
       <c r="D23" s="3" t="s">
@@ -2322,15 +2413,18 @@
       <c r="E23" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" ht="30" customHeight="1">
+      <c r="F23" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="30" customHeight="1">
       <c r="A24" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C24" s="27" t="s">
+      <c r="C24" s="20" t="s">
         <v>331</v>
       </c>
       <c r="D24" s="3" t="s">
@@ -2339,15 +2433,18 @@
       <c r="E24" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="F24" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C25" s="27" t="s">
+      <c r="C25" s="20" t="s">
         <v>331</v>
       </c>
       <c r="D25" s="3" t="s">
@@ -2356,15 +2453,18 @@
       <c r="E25" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="F25" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C26" s="31" t="s">
+      <c r="C26" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D26" s="3" t="s">
@@ -2373,15 +2473,18 @@
       <c r="E26" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" ht="30" customHeight="1">
+      <c r="F26" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="30" customHeight="1">
       <c r="A27" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C27" s="31" t="s">
+      <c r="C27" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D27" s="3" t="s">
@@ -2390,15 +2493,18 @@
       <c r="E27" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="28" spans="1:5">
+      <c r="F27" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C28" s="27" t="s">
+      <c r="C28" s="20" t="s">
         <v>332</v>
       </c>
       <c r="D28" s="3" t="s">
@@ -2407,15 +2513,18 @@
       <c r="E28" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="29" spans="1:5">
+      <c r="F28" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C29" s="27" t="s">
+      <c r="C29" s="20" t="s">
         <v>332</v>
       </c>
       <c r="D29" s="3" t="s">
@@ -2424,15 +2533,18 @@
       <c r="E29" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="30" spans="1:5">
+      <c r="F29" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C30" s="27" t="s">
+      <c r="C30" s="20" t="s">
         <v>332</v>
       </c>
       <c r="D30" s="3" t="s">
@@ -2441,15 +2553,18 @@
       <c r="E30" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="31" spans="1:5">
+      <c r="F30" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C31" s="27" t="s">
+      <c r="C31" s="20" t="s">
         <v>325</v>
       </c>
       <c r="D31" s="3" t="s">
@@ -2458,15 +2573,18 @@
       <c r="E31" s="3" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="32" spans="1:5">
+      <c r="F31" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C32" s="27" t="s">
+      <c r="C32" s="20" t="s">
         <v>325</v>
       </c>
       <c r="D32" s="3" t="s">
@@ -2475,15 +2593,18 @@
       <c r="E32" s="3" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="33" spans="1:5">
+      <c r="F32" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C33" s="27" t="s">
+      <c r="C33" s="20" t="s">
         <v>325</v>
       </c>
       <c r="D33" s="3" t="s">
@@ -2492,15 +2613,18 @@
       <c r="E33" s="3" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="34" spans="1:5">
+      <c r="F33" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C34" s="27" t="s">
+      <c r="C34" s="20" t="s">
         <v>325</v>
       </c>
       <c r="D34" s="3" t="s">
@@ -2509,15 +2633,18 @@
       <c r="E34" s="3" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="35" spans="1:5">
+      <c r="F34" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C35" s="27" t="s">
+      <c r="C35" s="20" t="s">
         <v>325</v>
       </c>
       <c r="D35" s="3" t="s">
@@ -2526,15 +2653,18 @@
       <c r="E35" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="36" spans="1:5">
+      <c r="F35" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C36" s="31" t="s">
+      <c r="C36" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D36" s="3" t="s">
@@ -2543,15 +2673,18 @@
       <c r="E36" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="37" spans="1:5">
+      <c r="F36" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C37" s="31" t="s">
+      <c r="C37" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D37" s="3" t="s">
@@ -2560,15 +2693,18 @@
       <c r="E37" s="3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="38" spans="1:5">
+      <c r="F37" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C38" s="31" t="s">
+      <c r="C38" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D38" s="3" t="s">
@@ -2577,15 +2713,18 @@
       <c r="E38" s="3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="39" spans="1:5">
+      <c r="F38" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C39" s="31" t="s">
+      <c r="C39" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D39" s="3" t="s">
@@ -2594,15 +2733,18 @@
       <c r="E39" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="40" spans="1:5">
+      <c r="F39" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C40" s="31" t="s">
+      <c r="C40" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D40" s="3" t="s">
@@ -2611,15 +2753,18 @@
       <c r="E40" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="41" spans="1:5">
+      <c r="F40" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C41" s="31" t="s">
+      <c r="C41" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D41" s="3" t="s">
@@ -2628,15 +2773,18 @@
       <c r="E41" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="42" spans="1:5">
+      <c r="F41" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C42" s="31" t="s">
+      <c r="C42" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D42" s="3" t="s">
@@ -2645,15 +2793,18 @@
       <c r="E42" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="43" spans="1:5">
+      <c r="F42" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C43" s="31" t="s">
+      <c r="C43" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D43" s="3" t="s">
@@ -2662,15 +2813,18 @@
       <c r="E43" s="3" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="44" spans="1:5">
+      <c r="F43" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C44" s="31" t="s">
+      <c r="C44" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D44" s="3" t="s">
@@ -2679,15 +2833,18 @@
       <c r="E44" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" ht="30" customHeight="1">
+      <c r="F44" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="30" customHeight="1">
       <c r="A45" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C45" s="31" t="s">
+      <c r="C45" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D45" s="3" t="s">
@@ -2696,15 +2853,18 @@
       <c r="E45" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="46" spans="1:5">
+      <c r="F45" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C46" s="31" t="s">
+      <c r="C46" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D46" s="3" t="s">
@@ -2713,15 +2873,18 @@
       <c r="E46" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="47" spans="1:5">
+      <c r="F46" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C47" s="27" t="s">
+      <c r="C47" s="20" t="s">
         <v>331</v>
       </c>
       <c r="D47" s="3" t="s">
@@ -2730,15 +2893,18 @@
       <c r="E47" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="48" spans="1:5">
+      <c r="F47" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
       <c r="A48" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C48" s="27" t="s">
+      <c r="C48" s="20" t="s">
         <v>331</v>
       </c>
       <c r="D48" s="3" t="s">
@@ -2747,15 +2913,18 @@
       <c r="E48" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="49" spans="1:5">
+      <c r="F48" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
       <c r="A49" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C49" s="27" t="s">
+      <c r="C49" s="20" t="s">
         <v>331</v>
       </c>
       <c r="D49" s="3" t="s">
@@ -2764,15 +2933,18 @@
       <c r="E49" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="50" spans="1:5">
+      <c r="F49" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
       <c r="A50" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C50" s="27" t="s">
+      <c r="C50" s="20" t="s">
         <v>331</v>
       </c>
       <c r="D50" s="3" t="s">
@@ -2781,15 +2953,18 @@
       <c r="E50" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="51" spans="1:5">
+      <c r="F50" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
       <c r="A51" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C51" s="27" t="s">
+      <c r="C51" s="20" t="s">
         <v>328</v>
       </c>
       <c r="D51" s="3" t="s">
@@ -2798,15 +2973,18 @@
       <c r="E51" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="52" spans="1:5">
+      <c r="F51" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
       <c r="A52" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C52" s="27" t="s">
+      <c r="C52" s="20" t="s">
         <v>328</v>
       </c>
       <c r="D52" s="3" t="s">
@@ -2815,15 +2993,18 @@
       <c r="E52" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="53" spans="1:5">
+      <c r="F52" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
       <c r="A53" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C53" s="27" t="s">
+      <c r="C53" s="20" t="s">
         <v>328</v>
       </c>
       <c r="D53" s="3" t="s">
@@ -2832,15 +3013,18 @@
       <c r="E53" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="54" spans="1:5">
+      <c r="F53" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
       <c r="A54" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C54" s="31" t="s">
+      <c r="C54" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D54" s="3" t="s">
@@ -2849,15 +3033,18 @@
       <c r="E54" s="3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="55" spans="1:5">
+      <c r="F54" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
       <c r="A55" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C55" s="31" t="s">
+      <c r="C55" s="3" t="s">
         <v>332</v>
       </c>
       <c r="D55" s="3" t="s">
@@ -2866,15 +3053,18 @@
       <c r="E55" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="56" spans="1:5">
+      <c r="F55" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
       <c r="A56" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C56" s="31" t="s">
+      <c r="C56" s="3" t="s">
         <v>332</v>
       </c>
       <c r="D56" s="3" t="s">
@@ -2883,15 +3073,18 @@
       <c r="E56" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="57" spans="1:5">
+      <c r="F56" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
       <c r="A57" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C57" s="27" t="s">
+      <c r="C57" s="20" t="s">
         <v>325</v>
       </c>
       <c r="D57" s="3" t="s">
@@ -2900,15 +3093,18 @@
       <c r="E57" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="58" spans="1:5">
+      <c r="F57" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
       <c r="A58" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C58" s="27" t="s">
+      <c r="C58" s="20" t="s">
         <v>325</v>
       </c>
       <c r="D58" s="3" t="s">
@@ -2917,15 +3113,18 @@
       <c r="E58" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="59" spans="1:5">
+      <c r="F58" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
       <c r="A59" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C59" s="27" t="s">
+      <c r="C59" s="20" t="s">
         <v>325</v>
       </c>
       <c r="D59" s="3" t="s">
@@ -2934,15 +3133,18 @@
       <c r="E59" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="60" spans="1:5">
+      <c r="F59" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
       <c r="A60" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C60" s="27" t="s">
+      <c r="C60" s="20" t="s">
         <v>325</v>
       </c>
       <c r="D60" s="3" t="s">
@@ -2951,15 +3153,18 @@
       <c r="E60" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="61" spans="1:5">
+      <c r="F60" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
       <c r="A61" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C61" s="27" t="s">
+      <c r="C61" s="20" t="s">
         <v>325</v>
       </c>
       <c r="D61" s="3" t="s">
@@ -2968,15 +3173,18 @@
       <c r="E61" s="3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="62" spans="1:5">
+      <c r="F61" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
       <c r="A62" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C62" s="27" t="s">
+      <c r="C62" s="20" t="s">
         <v>325</v>
       </c>
       <c r="D62" s="3" t="s">
@@ -2985,15 +3193,18 @@
       <c r="E62" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" ht="30" customHeight="1">
+      <c r="F62" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="30" customHeight="1">
       <c r="A63" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C63" s="27" t="s">
+      <c r="C63" s="20" t="s">
         <v>330</v>
       </c>
       <c r="D63" s="3" t="s">
@@ -3002,15 +3213,18 @@
       <c r="E63" s="3" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" ht="30" customHeight="1">
+      <c r="F63" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="30" customHeight="1">
       <c r="A64" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C64" s="27" t="s">
+      <c r="C64" s="20" t="s">
         <v>330</v>
       </c>
       <c r="D64" s="3" t="s">
@@ -3019,15 +3233,18 @@
       <c r="E64" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="65" spans="1:5">
+      <c r="F64" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
       <c r="A65" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C65" s="27" t="s">
+      <c r="C65" s="20" t="s">
         <v>333</v>
       </c>
       <c r="D65" s="3" t="s">
@@ -3036,15 +3253,18 @@
       <c r="E65" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="66" spans="1:5">
+      <c r="F65" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
       <c r="A66" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C66" s="27" t="s">
+      <c r="C66" s="20" t="s">
         <v>333</v>
       </c>
       <c r="D66" s="3" t="s">
@@ -3053,15 +3273,18 @@
       <c r="E66" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="67" spans="1:5">
+      <c r="F66" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
       <c r="A67" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C67" s="31" t="s">
+      <c r="C67" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D67" s="3" t="s">
@@ -3070,15 +3293,18 @@
       <c r="E67" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="68" spans="1:5">
+      <c r="F67" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
       <c r="A68" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C68" s="31" t="s">
+      <c r="C68" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D68" s="3" t="s">
@@ -3087,15 +3313,18 @@
       <c r="E68" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="69" spans="1:5">
+      <c r="F68" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
       <c r="A69" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C69" s="31" t="s">
+      <c r="C69" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D69" s="3" t="s">
@@ -3104,15 +3333,18 @@
       <c r="E69" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="70" spans="1:5">
+      <c r="F69" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
       <c r="A70" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C70" s="31" t="s">
+      <c r="C70" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D70" s="3" t="s">
@@ -3121,15 +3353,18 @@
       <c r="E70" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="71" spans="1:5">
+      <c r="F70" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
       <c r="A71" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C71" s="31" t="s">
+      <c r="C71" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D71" s="3" t="s">
@@ -3138,15 +3373,18 @@
       <c r="E71" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="72" spans="1:5">
+      <c r="F71" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
       <c r="A72" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C72" s="31" t="s">
+      <c r="C72" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D72" s="3" t="s">
@@ -3155,15 +3393,18 @@
       <c r="E72" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="73" spans="1:5">
+      <c r="F72" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
       <c r="A73" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C73" s="31" t="s">
+      <c r="C73" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D73" s="3" t="s">
@@ -3172,15 +3413,18 @@
       <c r="E73" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" ht="30" customHeight="1">
+      <c r="F73" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="30" customHeight="1">
       <c r="A74" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C74" s="27" t="s">
+      <c r="C74" s="20" t="s">
         <v>332</v>
       </c>
       <c r="D74" s="3" t="s">
@@ -3189,15 +3433,18 @@
       <c r="E74" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="75" spans="1:5">
+      <c r="F74" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
       <c r="A75" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="C75" s="31" t="s">
+      <c r="C75" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D75" s="3" t="s">
@@ -3206,15 +3453,18 @@
       <c r="E75" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" ht="30" customHeight="1">
+      <c r="F75" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="30" customHeight="1">
       <c r="A76" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C76" s="27" t="s">
+      <c r="C76" s="20" t="s">
         <v>331</v>
       </c>
       <c r="D76" s="3" t="s">
@@ -3223,15 +3473,18 @@
       <c r="E76" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="77" spans="1:5">
+      <c r="F76" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
       <c r="A77" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C77" s="27" t="s">
+      <c r="C77" s="20" t="s">
         <v>325</v>
       </c>
       <c r="D77" s="3" t="s">
@@ -3240,15 +3493,18 @@
       <c r="E77" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="78" spans="1:5">
+      <c r="F77" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
       <c r="A78" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C78" s="31" t="s">
+      <c r="C78" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D78" s="3" t="s">
@@ -3257,15 +3513,18 @@
       <c r="E78" s="3" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="79" spans="1:5">
+      <c r="F78" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
       <c r="A79" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C79" s="27" t="s">
+      <c r="C79" s="20" t="s">
         <v>334</v>
       </c>
       <c r="D79" s="3" t="s">
@@ -3274,15 +3533,18 @@
       <c r="E79" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="80" spans="1:5">
+      <c r="F79" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
       <c r="A80" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C80" s="27" t="s">
+      <c r="C80" s="20" t="s">
         <v>334</v>
       </c>
       <c r="D80" s="3" t="s">
@@ -3291,15 +3553,18 @@
       <c r="E80" s="3" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" ht="45" customHeight="1">
+      <c r="F80" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="45" customHeight="1">
       <c r="A81" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C81" s="27" t="s">
+      <c r="C81" s="20" t="s">
         <v>325</v>
       </c>
       <c r="D81" s="3" t="s">
@@ -3308,15 +3573,18 @@
       <c r="E81" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" ht="45" customHeight="1">
+      <c r="F81" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="45" customHeight="1">
       <c r="A82" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C82" s="31" t="s">
+      <c r="C82" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D82" s="3" t="s">
@@ -3325,15 +3593,18 @@
       <c r="E82" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" ht="45" customHeight="1">
+      <c r="F82" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="45" customHeight="1">
       <c r="A83" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C83" s="31" t="s">
+      <c r="C83" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D83" s="3" t="s">
@@ -3342,15 +3613,18 @@
       <c r="E83" s="3" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" ht="45" customHeight="1">
+      <c r="F83" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="45" customHeight="1">
       <c r="A84" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C84" s="31" t="s">
+      <c r="C84" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D84" s="3" t="s">
@@ -3359,15 +3633,18 @@
       <c r="E84" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" ht="45" customHeight="1">
+      <c r="F84" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="45" customHeight="1">
       <c r="A85" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="C85" s="31" t="s">
+      <c r="C85" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D85" s="3" t="s">
@@ -3376,15 +3653,18 @@
       <c r="E85" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" ht="45" customHeight="1">
+      <c r="F85" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="45" customHeight="1">
       <c r="A86" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="C86" s="31" t="s">
+      <c r="C86" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D86" s="3" t="s">
@@ -3393,15 +3673,18 @@
       <c r="E86" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" ht="45" customHeight="1">
+      <c r="F86" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="45" customHeight="1">
       <c r="A87" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="C87" s="31" t="s">
+      <c r="C87" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D87" s="3" t="s">
@@ -3410,15 +3693,18 @@
       <c r="E87" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" ht="45" customHeight="1">
+      <c r="F87" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="45" customHeight="1">
       <c r="A88" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="C88" s="31" t="s">
+      <c r="C88" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D88" s="3" t="s">
@@ -3427,15 +3713,18 @@
       <c r="E88" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" ht="45" customHeight="1">
+      <c r="F88" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="45" customHeight="1">
       <c r="A89" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="C89" s="31" t="s">
+      <c r="C89" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D89" s="3" t="s">
@@ -3444,15 +3733,18 @@
       <c r="E89" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" ht="45" customHeight="1">
+      <c r="F89" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="45" customHeight="1">
       <c r="A90" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="C90" s="31" t="s">
+      <c r="C90" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D90" s="3" t="s">
@@ -3461,15 +3753,18 @@
       <c r="E90" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" ht="45" customHeight="1">
+      <c r="F90" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="45" customHeight="1">
       <c r="A91" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="C91" s="31" t="s">
+      <c r="C91" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D91" s="3" t="s">
@@ -3478,15 +3773,18 @@
       <c r="E91" s="3" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" ht="45" customHeight="1">
+      <c r="F91" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="45" customHeight="1">
       <c r="A92" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="C92" s="31" t="s">
+      <c r="C92" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D92" s="3" t="s">
@@ -3495,15 +3793,18 @@
       <c r="E92" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" ht="45" customHeight="1">
+      <c r="F92" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="45" customHeight="1">
       <c r="A93" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="C93" s="31" t="s">
+      <c r="C93" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D93" s="3" t="s">
@@ -3512,15 +3813,18 @@
       <c r="E93" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="94" spans="1:5" ht="60" customHeight="1">
+      <c r="F93" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="60" customHeight="1">
       <c r="A94" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="C94" s="31" t="s">
+      <c r="C94" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D94" s="3" t="s">
@@ -3529,15 +3833,18 @@
       <c r="E94" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="95" spans="1:5" ht="45" customHeight="1">
+      <c r="F94" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="45" customHeight="1">
       <c r="A95" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="C95" s="31" t="s">
+      <c r="C95" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D95" s="3" t="s">
@@ -3546,15 +3853,18 @@
       <c r="E95" s="3" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="96" spans="1:5" ht="45" customHeight="1">
+      <c r="F95" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="45" customHeight="1">
       <c r="A96" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="C96" s="31" t="s">
+      <c r="C96" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D96" s="3" t="s">
@@ -3563,15 +3873,18 @@
       <c r="E96" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="97" spans="1:5" ht="45" customHeight="1">
+      <c r="F96" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="45" customHeight="1">
       <c r="A97" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="C97" s="31" t="s">
+      <c r="C97" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D97" s="3" t="s">
@@ -3580,15 +3893,18 @@
       <c r="E97" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="98" spans="1:5">
+      <c r="F97" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
       <c r="A98" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C98" s="31" t="s">
+      <c r="C98" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D98" s="3" t="s">
@@ -3597,15 +3913,18 @@
       <c r="E98" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="99" spans="1:5">
+      <c r="F98" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
       <c r="A99" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C99" s="31" t="s">
+      <c r="C99" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D99" s="3" t="s">
@@ -3614,15 +3933,18 @@
       <c r="E99" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="100" spans="1:5">
+      <c r="F99" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
       <c r="A100" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="C100" s="31" t="s">
+      <c r="C100" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D100" s="3" t="s">
@@ -3631,15 +3953,18 @@
       <c r="E100" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="101" spans="1:5">
+      <c r="F100" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
       <c r="A101" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="C101" s="31" t="s">
+      <c r="C101" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D101" s="3" t="s">
@@ -3648,15 +3973,18 @@
       <c r="E101" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="102" spans="1:5" ht="30" customHeight="1">
+      <c r="F101" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="30" customHeight="1">
       <c r="A102" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="C102" s="27" t="s">
+      <c r="C102" s="20" t="s">
         <v>333</v>
       </c>
       <c r="D102" s="3" t="s">
@@ -3665,15 +3993,18 @@
       <c r="E102" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="103" spans="1:5" ht="30" customHeight="1">
+      <c r="F102" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="30" customHeight="1">
       <c r="A103" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="C103" s="27" t="s">
+      <c r="C103" s="20" t="s">
         <v>325</v>
       </c>
       <c r="D103" s="3" t="s">
@@ -3682,15 +4013,18 @@
       <c r="E103" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="104" spans="1:5">
+      <c r="F103" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
       <c r="A104" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C104" s="27" t="s">
+      <c r="C104" s="20" t="s">
         <v>329</v>
       </c>
       <c r="D104" s="3" t="s">
@@ -3699,15 +4033,18 @@
       <c r="E104" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="105" spans="1:5">
+      <c r="F104" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
       <c r="A105" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C105" s="27" t="s">
+      <c r="C105" s="20" t="s">
         <v>335</v>
       </c>
       <c r="D105" s="3" t="s">
@@ -3716,15 +4053,18 @@
       <c r="E105" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="106" spans="1:5">
+      <c r="F105" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
       <c r="A106" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C106" s="27" t="s">
+      <c r="C106" s="20" t="s">
         <v>327</v>
       </c>
       <c r="D106" s="3" t="s">
@@ -3733,15 +4073,18 @@
       <c r="E106" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="107" spans="1:5">
+      <c r="F106" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
       <c r="A107" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C107" s="27" t="s">
+      <c r="C107" s="20" t="s">
         <v>331</v>
       </c>
       <c r="D107" s="3" t="s">
@@ -3750,15 +4093,18 @@
       <c r="E107" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="108" spans="1:5">
+      <c r="F107" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
       <c r="A108" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C108" s="31" t="s">
+      <c r="C108" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D108" s="3" t="s">
@@ -3767,15 +4113,18 @@
       <c r="E108" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="109" spans="1:5">
+      <c r="F108" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
       <c r="A109" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="C109" s="27" t="s">
+      <c r="C109" s="20" t="s">
         <v>328</v>
       </c>
       <c r="D109" s="3" t="s">
@@ -3784,15 +4133,18 @@
       <c r="E109" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="110" spans="1:5">
+      <c r="F109" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
       <c r="A110" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="C110" s="31" t="s">
+      <c r="C110" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D110" s="3" t="s">
@@ -3801,15 +4153,18 @@
       <c r="E110" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="111" spans="1:5">
+      <c r="F110" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
       <c r="A111" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="C111" s="31" t="s">
+      <c r="C111" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D111" s="3" t="s">
@@ -3818,15 +4173,18 @@
       <c r="E111" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="112" spans="1:5">
+      <c r="F111" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
       <c r="A112" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="C112" s="31" t="s">
+      <c r="C112" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D112" s="3" t="s">
@@ -3835,15 +4193,18 @@
       <c r="E112" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="113" spans="1:5">
+      <c r="F112" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
       <c r="A113" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="C113" s="31" t="s">
+      <c r="C113" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D113" s="3" t="s">
@@ -3852,15 +4213,18 @@
       <c r="E113" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="114" spans="1:5" ht="30" customHeight="1">
+      <c r="F113" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" ht="30" customHeight="1">
       <c r="A114" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="C114" s="31" t="s">
+      <c r="C114" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D114" s="3" t="s">
@@ -3869,15 +4233,18 @@
       <c r="E114" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="115" spans="1:5" ht="45" customHeight="1">
+      <c r="F114" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="45" customHeight="1">
       <c r="A115" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B115" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="C115" s="27" t="s">
+      <c r="C115" s="20" t="s">
         <v>325</v>
       </c>
       <c r="D115" s="3" t="s">
@@ -3886,15 +4253,18 @@
       <c r="E115" s="3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="116" spans="1:5" ht="30" customHeight="1">
+      <c r="F115" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="30" customHeight="1">
       <c r="A116" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B116" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="C116" s="31" t="s">
+      <c r="C116" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D116" s="3" t="s">
@@ -3903,15 +4273,18 @@
       <c r="E116" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="117" spans="1:5">
+      <c r="F116" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
       <c r="A117" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C117" s="31" t="s">
+      <c r="C117" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D117" s="3" t="s">
@@ -3920,15 +4293,18 @@
       <c r="E117" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="118" spans="1:5">
+      <c r="F117" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
       <c r="A118" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B118" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C118" s="31" t="s">
+      <c r="C118" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D118" s="3" t="s">
@@ -3937,15 +4313,18 @@
       <c r="E118" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="119" spans="1:5">
+      <c r="F118" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
       <c r="A119" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C119" s="31" t="s">
+      <c r="C119" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D119" s="3" t="s">
@@ -3954,15 +4333,18 @@
       <c r="E119" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="120" spans="1:5">
+      <c r="F119" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
       <c r="A120" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B120" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C120" s="31" t="s">
+      <c r="C120" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D120" s="3" t="s">
@@ -3971,15 +4353,18 @@
       <c r="E120" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="121" spans="1:5" ht="30" customHeight="1">
+      <c r="F120" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="30" customHeight="1">
       <c r="A121" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="C121" s="31" t="s">
+      <c r="C121" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D121" s="3" t="s">
@@ -3988,15 +4373,18 @@
       <c r="E121" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="122" spans="1:5">
+      <c r="F121" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
       <c r="A122" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="C122" s="31" t="s">
+      <c r="C122" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D122" s="3" t="s">
@@ -4005,15 +4393,18 @@
       <c r="E122" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="123" spans="1:5" ht="30" customHeight="1">
+      <c r="F122" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" ht="30" customHeight="1">
       <c r="A123" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="C123" s="31" t="s">
+      <c r="C123" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D123" s="3" t="s">
@@ -4022,15 +4413,18 @@
       <c r="E123" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="124" spans="1:5" ht="45" customHeight="1">
+      <c r="F123" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" ht="45" customHeight="1">
       <c r="A124" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="C124" s="31" t="s">
+      <c r="C124" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D124" s="3" t="s">
@@ -4039,15 +4433,18 @@
       <c r="E124" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="125" spans="1:5">
+      <c r="F124" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
       <c r="A125" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="C125" s="31" t="s">
+      <c r="C125" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D125" s="3" t="s">
@@ -4056,15 +4453,18 @@
       <c r="E125" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="126" spans="1:5">
+      <c r="F125" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
       <c r="A126" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="C126" s="31" t="s">
+      <c r="C126" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D126" s="3" t="s">
@@ -4073,15 +4473,18 @@
       <c r="E126" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="127" spans="1:5">
+      <c r="F126" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
       <c r="A127" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="C127" s="31" t="s">
+      <c r="C127" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D127" s="3" t="s">
@@ -4090,15 +4493,18 @@
       <c r="E127" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="128" spans="1:5">
+      <c r="F127" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
       <c r="A128" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="C128" s="31" t="s">
+      <c r="C128" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D128" s="3" t="s">
@@ -4107,15 +4513,18 @@
       <c r="E128" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="129" spans="1:5">
+      <c r="F128" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
       <c r="A129" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="C129" s="31" t="s">
+      <c r="C129" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D129" s="3" t="s">
@@ -4124,15 +4533,18 @@
       <c r="E129" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="130" spans="1:5">
+      <c r="F129" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
       <c r="A130" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="C130" s="31" t="s">
+      <c r="C130" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D130" s="3" t="s">
@@ -4141,15 +4553,18 @@
       <c r="E130" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="131" spans="1:5">
+      <c r="F130" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
       <c r="A131" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="C131" s="31" t="s">
+      <c r="C131" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D131" s="3" t="s">
@@ -4158,15 +4573,18 @@
       <c r="E131" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="132" spans="1:5" ht="30" customHeight="1">
+      <c r="F131" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" ht="30" customHeight="1">
       <c r="A132" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="C132" s="31" t="s">
+      <c r="C132" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D132" s="3" t="s">
@@ -4175,15 +4593,18 @@
       <c r="E132" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="133" spans="1:5" ht="30" customHeight="1">
+      <c r="F132" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" ht="30" customHeight="1">
       <c r="A133" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B133" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="C133" s="31" t="s">
+      <c r="C133" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D133" s="3" t="s">
@@ -4192,15 +4613,18 @@
       <c r="E133" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="134" spans="1:5">
+      <c r="F133" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
       <c r="A134" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="C134" s="31" t="s">
+      <c r="C134" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D134" s="3" t="s">
@@ -4209,15 +4633,18 @@
       <c r="E134" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="135" spans="1:5">
+      <c r="F134" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6">
       <c r="A135" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="C135" s="31" t="s">
+      <c r="C135" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D135" s="3" t="s">
@@ -4226,15 +4653,18 @@
       <c r="E135" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="136" spans="1:5" ht="30">
+      <c r="F135" s="36">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" ht="30">
       <c r="A136" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="C136" s="31" t="s">
+      <c r="C136" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D136" s="3" t="s">
@@ -4243,15 +4673,18 @@
       <c r="E136" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="137" spans="1:5" ht="30">
+      <c r="F136" s="36">
+        <v>46315</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" ht="30">
       <c r="A137" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="C137" s="31" t="s">
+      <c r="C137" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D137" s="3" t="s">
@@ -4260,15 +4693,18 @@
       <c r="E137" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="138" spans="1:5" ht="30">
+      <c r="F137" s="36">
+        <v>46315</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="30">
       <c r="A138" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C138" s="27" t="s">
+      <c r="C138" s="20" t="s">
         <v>330</v>
       </c>
       <c r="D138" s="3" t="s">
@@ -4277,15 +4713,18 @@
       <c r="E138" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="139" spans="1:5">
+      <c r="F138" s="36">
+        <v>46315</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
       <c r="A139" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C139" s="27" t="s">
+      <c r="C139" s="20" t="s">
         <v>329</v>
       </c>
       <c r="D139" s="3" t="s">
@@ -4294,15 +4733,18 @@
       <c r="E139" s="3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="140" spans="1:5">
+      <c r="F139" s="36">
+        <v>46315</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6">
       <c r="A140" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C140" s="27" t="s">
+      <c r="C140" s="20" t="s">
         <v>331</v>
       </c>
       <c r="D140" s="3" t="s">
@@ -4311,15 +4753,18 @@
       <c r="E140" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="141" spans="1:5" ht="30">
+      <c r="F140" s="36">
+        <v>46315</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" ht="30">
       <c r="A141" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C141" s="27" t="s">
+      <c r="C141" s="20" t="s">
         <v>328</v>
       </c>
       <c r="D141" s="3" t="s">
@@ -4328,15 +4773,18 @@
       <c r="E141" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="142" spans="1:5" ht="30">
+      <c r="F141" s="36">
+        <v>46315</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="30">
       <c r="A142" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C142" s="27" t="s">
+      <c r="C142" s="20" t="s">
         <v>328</v>
       </c>
       <c r="D142" s="3" t="s">
@@ -4345,15 +4793,18 @@
       <c r="E142" s="3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="143" spans="1:5" ht="30">
+      <c r="F142" s="36">
+        <v>46315</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" ht="30">
       <c r="A143" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C143" s="27" t="s">
+      <c r="C143" s="20" t="s">
         <v>335</v>
       </c>
       <c r="D143" s="3" t="s">
@@ -4362,15 +4813,18 @@
       <c r="E143" s="3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="144" spans="1:5">
+      <c r="F143" s="36">
+        <v>46315</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
       <c r="A144" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B144" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="C144" s="27" t="s">
+      <c r="C144" s="20" t="s">
         <v>330</v>
       </c>
       <c r="D144" s="3" t="s">
@@ -4378,6 +4832,9 @@
       </c>
       <c r="E144" s="3" t="s">
         <v>45</v>
+      </c>
+      <c r="F144" s="36">
+        <v>46315</v>
       </c>
     </row>
   </sheetData>
@@ -4429,13 +4886,13 @@
       <c r="D1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="14" t="s">
         <v>287</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="G1" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="H1" s="33" t="s">
+      <c r="H1" s="24" t="s">
         <v>338</v>
       </c>
     </row>
@@ -4457,11 +4914,11 @@
         <f t="array" ref="F2:F4">_xlfn._xlws.SORT(_xlfn.UNIQUE(業者來源索引[業別]))</f>
         <v>保險業</v>
       </c>
-      <c r="G2" s="22" t="str" cm="1">
+      <c r="G2" s="16" t="str" cm="1">
         <f t="array" ref="G2:G83">_xlfn._xlws.SORT(_xlfn.UNIQUE(業者來源索引[業者]))</f>
         <v>口袋證券</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="H2" s="17" t="s">
         <v>294</v>
       </c>
     </row>
@@ -4482,10 +4939,10 @@
       <c r="F3" t="str">
         <v>銀行業</v>
       </c>
-      <c r="G3" s="22" t="str">
+      <c r="G3" s="16" t="str">
         <v>大昌證券</v>
       </c>
-      <c r="H3" s="23" t="s">
+      <c r="H3" s="17" t="s">
         <v>296</v>
       </c>
     </row>
@@ -4506,10 +4963,10 @@
       <c r="F4" t="str">
         <v>證券期貨業</v>
       </c>
-      <c r="G4" s="22" t="str">
+      <c r="G4" s="16" t="str">
         <v>中信產險</v>
       </c>
-      <c r="H4" s="23" t="s">
+      <c r="H4" s="17" t="s">
         <v>299</v>
       </c>
     </row>
@@ -4527,10 +4984,10 @@
         <f>COUNTIFS(AI應用場景!A:A,A5,AI應用場景!B:B,B5)</f>
         <v>1</v>
       </c>
-      <c r="G5" s="22" t="str">
+      <c r="G5" s="16" t="str">
         <v>中國信託銀行</v>
       </c>
-      <c r="H5" s="23" t="s">
+      <c r="H5" s="17" t="s">
         <v>301</v>
       </c>
     </row>
@@ -4548,10 +5005,10 @@
         <f>COUNTIFS(AI應用場景!A:A,A6,AI應用場景!B:B,B6)</f>
         <v>1</v>
       </c>
-      <c r="G6" s="22" t="str">
+      <c r="G6" s="16" t="str">
         <v>元大人壽</v>
       </c>
-      <c r="H6" s="23" t="s">
+      <c r="H6" s="17" t="s">
         <v>304</v>
       </c>
     </row>
@@ -4569,10 +5026,10 @@
         <f>COUNTIFS(AI應用場景!A:A,A7,AI應用場景!B:B,B7)</f>
         <v>5</v>
       </c>
-      <c r="G7" s="22" t="str">
+      <c r="G7" s="16" t="str">
         <v>元大銀行</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="H7" s="17" t="s">
         <v>306</v>
       </c>
     </row>
@@ -4590,10 +5047,10 @@
         <f>COUNTIFS(AI應用場景!A:A,A8,AI應用場景!B:B,B8)</f>
         <v>1</v>
       </c>
-      <c r="G8" s="22" t="str">
+      <c r="G8" s="16" t="str">
         <v>元大證券</v>
       </c>
-      <c r="H8" s="23" t="s">
+      <c r="H8" s="17" t="s">
         <v>309</v>
       </c>
     </row>
@@ -4611,10 +5068,10 @@
         <f>COUNTIFS(AI應用場景!A:A,A9,AI應用場景!B:B,B9)</f>
         <v>1</v>
       </c>
-      <c r="G9" s="22" t="str">
+      <c r="G9" s="16" t="str">
         <v>公勝保險經紀人股份有限公司</v>
       </c>
-      <c r="H9" s="23" t="s">
+      <c r="H9" s="17" t="s">
         <v>311</v>
       </c>
     </row>
@@ -4632,10 +5089,10 @@
         <f>COUNTIFS(AI應用場景!A:A,A10,AI應用場景!B:B,B10)</f>
         <v>1</v>
       </c>
-      <c r="G10" s="22" t="str">
+      <c r="G10" s="16" t="str">
         <v>友邦人壽</v>
       </c>
-      <c r="H10" s="23" t="s">
+      <c r="H10" s="17" t="s">
         <v>313</v>
       </c>
     </row>
@@ -4653,10 +5110,10 @@
         <f>COUNTIFS(AI應用場景!A:A,A11,AI應用場景!B:B,B11)</f>
         <v>6</v>
       </c>
-      <c r="G11" s="22" t="str">
+      <c r="G11" s="16" t="str">
         <v>王道銀行</v>
       </c>
-      <c r="H11" s="23" t="s">
+      <c r="H11" s="17" t="s">
         <v>315</v>
       </c>
     </row>
@@ -4674,10 +5131,10 @@
         <f>COUNTIFS(AI應用場景!A:A,A12,AI應用場景!B:B,B12)</f>
         <v>1</v>
       </c>
-      <c r="G12" s="22" t="str">
+      <c r="G12" s="16" t="str">
         <v>台中銀行</v>
       </c>
-      <c r="H12" s="23" t="s">
+      <c r="H12" s="17" t="s">
         <v>317</v>
       </c>
     </row>
@@ -4695,10 +5152,10 @@
         <f>COUNTIFS(AI應用場景!A:A,A13,AI應用場景!B:B,B13)</f>
         <v>1</v>
       </c>
-      <c r="G13" s="22" t="str">
+      <c r="G13" s="16" t="str">
         <v>台北富邦銀行</v>
       </c>
-      <c r="H13" s="23" t="s">
+      <c r="H13" s="17" t="s">
         <v>319</v>
       </c>
     </row>
@@ -4716,10 +5173,10 @@
         <f>COUNTIFS(AI應用場景!A:A,A14,AI應用場景!B:B,B14)</f>
         <v>1</v>
       </c>
-      <c r="G14" s="22" t="str">
+      <c r="G14" s="16" t="str">
         <v>台新銀行</v>
       </c>
-      <c r="H14" s="23" t="s">
+      <c r="H14" s="17" t="s">
         <v>321</v>
       </c>
     </row>
@@ -4737,10 +5194,10 @@
         <f>COUNTIFS(AI應用場景!A:A,A15,AI應用場景!B:B,B15)</f>
         <v>2</v>
       </c>
-      <c r="G15" s="22" t="str">
+      <c r="G15" s="16" t="str">
         <v>台新證券</v>
       </c>
-      <c r="H15" s="23" t="s">
+      <c r="H15" s="17" t="s">
         <v>336</v>
       </c>
     </row>
@@ -4758,10 +5215,10 @@
         <f>COUNTIFS(AI應用場景!A:A,A16,AI應用場景!B:B,B16)</f>
         <v>3</v>
       </c>
-      <c r="G16" s="22" t="str">
+      <c r="G16" s="16" t="str">
         <v>台灣人壽</v>
       </c>
-      <c r="H16" s="23" t="s">
+      <c r="H16" s="17" t="s">
         <v>322</v>
       </c>
     </row>
@@ -4779,7 +5236,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A17,AI應用場景!B:B,B17)</f>
         <v>1</v>
       </c>
-      <c r="G17" s="22" t="str">
+      <c r="G17" s="16" t="str">
         <v>永達保險經紀人股份有限公司</v>
       </c>
     </row>
@@ -4797,7 +5254,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A18,AI應用場景!B:B,B18)</f>
         <v>1</v>
       </c>
-      <c r="G18" s="22" t="str">
+      <c r="G18" s="16" t="str">
         <v>永豐金證券</v>
       </c>
     </row>
@@ -4815,7 +5272,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A19,AI應用場景!B:B,B19)</f>
         <v>3</v>
       </c>
-      <c r="G19" s="22" t="str">
+      <c r="G19" s="16" t="str">
         <v>玉山金控</v>
       </c>
     </row>
@@ -4833,7 +5290,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A20,AI應用場景!B:B,B20)</f>
         <v>5</v>
       </c>
-      <c r="G20" s="22" t="str">
+      <c r="G20" s="16" t="str">
         <v>玉山銀行</v>
       </c>
     </row>
@@ -4851,7 +5308,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A21,AI應用場景!B:B,B21)</f>
         <v>1</v>
       </c>
-      <c r="G21" s="22" t="str">
+      <c r="G21" s="16" t="str">
         <v>玉山證券</v>
       </c>
     </row>
@@ -4869,7 +5326,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A22,AI應用場景!B:B,B22)</f>
         <v>1</v>
       </c>
-      <c r="G22" s="22" t="str">
+      <c r="G22" s="16" t="str">
         <v>兆豐產險</v>
       </c>
     </row>
@@ -4887,7 +5344,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A23,AI應用場景!B:B,B23)</f>
         <v>2</v>
       </c>
-      <c r="G23" s="22" t="str">
+      <c r="G23" s="16" t="str">
         <v>全支付公司</v>
       </c>
     </row>
@@ -4905,7 +5362,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A24,AI應用場景!B:B,B24)</f>
         <v>1</v>
       </c>
-      <c r="G24" s="22" t="str">
+      <c r="G24" s="16" t="str">
         <v>全盈支付</v>
       </c>
     </row>
@@ -4923,7 +5380,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A25,AI應用場景!B:B,B25)</f>
         <v>4</v>
       </c>
-      <c r="G25" s="22" t="str">
+      <c r="G25" s="16" t="str">
         <v>全球人壽</v>
       </c>
     </row>
@@ -4941,7 +5398,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A26,AI應用場景!B:B,B26)</f>
         <v>2</v>
       </c>
-      <c r="G26" s="22" t="str">
+      <c r="G26" s="16" t="str">
         <v>存保公司</v>
       </c>
     </row>
@@ -4959,7 +5416,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A27,AI應用場景!B:B,B27)</f>
         <v>4</v>
       </c>
-      <c r="G27" s="22" t="str">
+      <c r="G27" s="16" t="str">
         <v>和安保險代理人股份有限公司</v>
       </c>
     </row>
@@ -4977,7 +5434,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A28,AI應用場景!B:B,B28)</f>
         <v>3</v>
       </c>
-      <c r="G28" s="22" t="str">
+      <c r="G28" s="16" t="str">
         <v>東方匯理投信</v>
       </c>
     </row>
@@ -4995,7 +5452,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A29,AI應用場景!B:B,B29)</f>
         <v>1</v>
       </c>
-      <c r="G29" s="22" t="str">
+      <c r="G29" s="16" t="str">
         <v>法盛投顧</v>
       </c>
     </row>
@@ -5013,7 +5470,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A30,AI應用場景!B:B,B30)</f>
         <v>2</v>
       </c>
-      <c r="G30" s="22" t="str">
+      <c r="G30" s="16" t="str">
         <v>金融研訓院</v>
       </c>
     </row>
@@ -5031,7 +5488,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A31,AI應用場景!B:B,B31)</f>
         <v>6</v>
       </c>
-      <c r="G31" s="22" t="str">
+      <c r="G31" s="16" t="str">
         <v>阿爾發投顧</v>
       </c>
     </row>
@@ -5049,7 +5506,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A32,AI應用場景!B:B,B32)</f>
         <v>2</v>
       </c>
-      <c r="G32" s="22" t="str">
+      <c r="G32" s="16" t="str">
         <v>保誠人壽</v>
       </c>
     </row>
@@ -5067,7 +5524,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A33,AI應用場景!B:B,B33)</f>
         <v>2</v>
       </c>
-      <c r="G33" s="22" t="str">
+      <c r="G33" s="16" t="str">
         <v>南山人壽</v>
       </c>
     </row>
@@ -5085,7 +5542,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A34,AI應用場景!B:B,B34)</f>
         <v>1</v>
       </c>
-      <c r="G34" s="22" t="str">
+      <c r="G34" s="16" t="str">
         <v>科法斯產險</v>
       </c>
     </row>
@@ -5103,7 +5560,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A35,AI應用場景!B:B,B35)</f>
         <v>4</v>
       </c>
-      <c r="G35" s="22" t="str">
+      <c r="G35" s="16" t="str">
         <v>科隆再保公司</v>
       </c>
     </row>
@@ -5121,7 +5578,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A36,AI應用場景!B:B,B36)</f>
         <v>1</v>
       </c>
-      <c r="G36" s="22" t="str">
+      <c r="G36" s="16" t="str">
         <v>美商達信保險經紀人股份有限公司台灣分公司</v>
       </c>
     </row>
@@ -5139,7 +5596,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A37,AI應用場景!B:B,B37)</f>
         <v>1</v>
       </c>
-      <c r="G37" s="22" t="str">
+      <c r="G37" s="16" t="str">
         <v>財團法人汽車交通事故特別補償基金</v>
       </c>
     </row>
@@ -5157,7 +5614,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A38,AI應用場景!B:B,B38)</f>
         <v>1</v>
       </c>
-      <c r="G38" s="22" t="str">
+      <c r="G38" s="16" t="str">
         <v>國泰人壽</v>
       </c>
     </row>
@@ -5175,7 +5632,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A39,AI應用場景!B:B,B39)</f>
         <v>1</v>
       </c>
-      <c r="G39" s="22" t="str">
+      <c r="G39" s="16" t="str">
         <v>國泰世華銀行</v>
       </c>
     </row>
@@ -5193,7 +5650,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A40,AI應用場景!B:B,B40)</f>
         <v>1</v>
       </c>
-      <c r="G40" s="22" t="str">
+      <c r="G40" s="16" t="str">
         <v>國泰產險</v>
       </c>
     </row>
@@ -5211,7 +5668,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A41,AI應用場景!B:B,B41)</f>
         <v>1</v>
       </c>
-      <c r="G41" s="22" t="str">
+      <c r="G41" s="16" t="str">
         <v>國泰證券</v>
       </c>
     </row>
@@ -5229,7 +5686,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A42,AI應用場景!B:B,B42)</f>
         <v>1</v>
       </c>
-      <c r="G42" s="22" t="str">
+      <c r="G42" s="16" t="str">
         <v>將來銀行</v>
       </c>
     </row>
@@ -5247,7 +5704,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A43,AI應用場景!B:B,B43)</f>
         <v>2</v>
       </c>
-      <c r="G43" s="22" t="str">
+      <c r="G43" s="16" t="str">
         <v>統一期貨</v>
       </c>
     </row>
@@ -5265,7 +5722,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A44,AI應用場景!B:B,B44)</f>
         <v>1</v>
       </c>
-      <c r="G44" s="22" t="str">
+      <c r="G44" s="16" t="str">
         <v>統一證券</v>
       </c>
     </row>
@@ -5283,7 +5740,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A45,AI應用場景!B:B,B45)</f>
         <v>2</v>
       </c>
-      <c r="G45" s="22" t="str">
+      <c r="G45" s="16" t="str">
         <v>連線銀行</v>
       </c>
     </row>
@@ -5301,7 +5758,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A46,AI應用場景!B:B,B46)</f>
         <v>1</v>
       </c>
-      <c r="G46" s="22" t="str">
+      <c r="G46" s="16" t="str">
         <v>野村投信</v>
       </c>
     </row>
@@ -5319,7 +5776,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A47,AI應用場景!B:B,B47)</f>
         <v>2</v>
       </c>
-      <c r="G47" s="22" t="str">
+      <c r="G47" s="16" t="str">
         <v>凱基人壽</v>
       </c>
     </row>
@@ -5337,7 +5794,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A48,AI應用場景!B:B,B48)</f>
         <v>3</v>
       </c>
-      <c r="G48" s="22" t="str">
+      <c r="G48" s="16" t="str">
         <v>凱基證券</v>
       </c>
     </row>
@@ -5355,7 +5812,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A49,AI應用場景!B:B,B49)</f>
         <v>4</v>
       </c>
-      <c r="G49" s="22" t="str">
+      <c r="G49" s="16" t="str">
         <v>富邦人壽</v>
       </c>
     </row>
@@ -5373,7 +5830,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A50,AI應用場景!B:B,B50)</f>
         <v>1</v>
       </c>
-      <c r="G50" s="22" t="str">
+      <c r="G50" s="16" t="str">
         <v>富邦金控</v>
       </c>
     </row>
@@ -5391,7 +5848,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A51,AI應用場景!B:B,B51)</f>
         <v>1</v>
       </c>
-      <c r="G51" s="22" t="str">
+      <c r="G51" s="16" t="str">
         <v>富邦產險</v>
       </c>
     </row>
@@ -5409,7 +5866,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A52,AI應用場景!B:B,B52)</f>
         <v>2</v>
       </c>
-      <c r="G52" s="22" t="str">
+      <c r="G52" s="16" t="str">
         <v>富邦期貨</v>
       </c>
     </row>
@@ -5427,7 +5884,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A53,AI應用場景!B:B,B53)</f>
         <v>2</v>
       </c>
-      <c r="G53" s="22" t="str">
+      <c r="G53" s="16" t="str">
         <v>富邦綜合保險代理人股份有限公司</v>
       </c>
     </row>
@@ -5445,7 +5902,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A54,AI應用場景!B:B,B54)</f>
         <v>1</v>
       </c>
-      <c r="G54" s="22" t="str">
+      <c r="G54" s="16" t="str">
         <v>富邦證券</v>
       </c>
     </row>
@@ -5463,7 +5920,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A55,AI應用場景!B:B,B55)</f>
         <v>1</v>
       </c>
-      <c r="G55" s="22" t="str">
+      <c r="G55" s="16" t="str">
         <v>富達投信</v>
       </c>
     </row>
@@ -5481,7 +5938,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A56,AI應用場景!B:B,B56)</f>
         <v>1</v>
       </c>
-      <c r="G56" s="22" t="str">
+      <c r="G56" s="16" t="str">
         <v>富蘭克林投顧</v>
       </c>
     </row>
@@ -5499,7 +5956,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A57,AI應用場景!B:B,B57)</f>
         <v>1</v>
       </c>
-      <c r="G57" s="22" t="str">
+      <c r="G57" s="16" t="str">
         <v>復華投信</v>
       </c>
     </row>
@@ -5517,7 +5974,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A58,AI應用場景!B:B,B58)</f>
         <v>1</v>
       </c>
-      <c r="G58" s="22" t="str">
+      <c r="G58" s="16" t="str">
         <v>景順投信</v>
       </c>
     </row>
@@ -5535,7 +5992,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A59,AI應用場景!B:B,B59)</f>
         <v>2</v>
       </c>
-      <c r="G59" s="22" t="str">
+      <c r="G59" s="16" t="str">
         <v>智匯保險經紀人股份有限公司</v>
       </c>
     </row>
@@ -5553,7 +6010,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A60,AI應用場景!B:B,B60)</f>
         <v>1</v>
       </c>
-      <c r="G60" s="22" t="str">
+      <c r="G60" s="16" t="str">
         <v>期貨交易所</v>
       </c>
     </row>
@@ -5571,7 +6028,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A61,AI應用場景!B:B,B61)</f>
         <v>1</v>
       </c>
-      <c r="G61" s="22" t="str">
+      <c r="G61" s="16" t="str">
         <v>渣打銀行</v>
       </c>
     </row>
@@ -5589,7 +6046,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A62,AI應用場景!B:B,B62)</f>
         <v>1</v>
       </c>
-      <c r="G62" s="22" t="str">
+      <c r="G62" s="16" t="str">
         <v>華南銀行</v>
       </c>
     </row>
@@ -5607,7 +6064,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A63,AI應用場景!B:B,B63)</f>
         <v>1</v>
       </c>
-      <c r="G63" s="22" t="str">
+      <c r="G63" s="16" t="str">
         <v>華南證券</v>
       </c>
     </row>
@@ -5625,7 +6082,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A64,AI應用場景!B:B,B64)</f>
         <v>4</v>
       </c>
-      <c r="G64" s="22" t="str">
+      <c r="G64" s="16" t="str">
         <v>新光人壽</v>
       </c>
     </row>
@@ -5643,7 +6100,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A65,AI應用場景!B:B,B65)</f>
         <v>1</v>
       </c>
-      <c r="G65" s="22" t="str">
+      <c r="G65" s="16" t="str">
         <v>新安東京產險</v>
       </c>
     </row>
@@ -5661,7 +6118,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A66,AI應用場景!B:B,B66)</f>
         <v>1</v>
       </c>
-      <c r="G66" s="22" t="str">
+      <c r="G66" s="16" t="str">
         <v>滙豐銀行</v>
       </c>
     </row>
@@ -5679,7 +6136,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A67,AI應用場景!B:B,B67)</f>
         <v>1</v>
       </c>
-      <c r="G67" s="22" t="str">
+      <c r="G67" s="16" t="str">
         <v>瑞銀投信</v>
       </c>
     </row>
@@ -5697,7 +6154,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A68,AI應用場景!B:B,B68)</f>
         <v>4</v>
       </c>
-      <c r="G68" s="22" t="str">
+      <c r="G68" s="16" t="str">
         <v>群益投信</v>
       </c>
     </row>
@@ -5715,7 +6172,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A69,AI應用場景!B:B,B69)</f>
         <v>1</v>
       </c>
-      <c r="G69" s="22" t="str">
+      <c r="G69" s="16" t="str">
         <v>群益期貨</v>
       </c>
     </row>
@@ -5733,7 +6190,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A70,AI應用場景!B:B,B70)</f>
         <v>1</v>
       </c>
-      <c r="G70" s="22" t="str">
+      <c r="G70" s="16" t="str">
         <v>路博邁投信</v>
       </c>
     </row>
@@ -5751,7 +6208,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A71,AI應用場景!B:B,B71)</f>
         <v>2</v>
       </c>
-      <c r="G71" s="22" t="str">
+      <c r="G71" s="16" t="str">
         <v>彰化銀行</v>
       </c>
     </row>
@@ -5769,7 +6226,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A72,AI應用場景!B:B,B72)</f>
         <v>1</v>
       </c>
-      <c r="G72" s="22" t="str">
+      <c r="G72" s="16" t="str">
         <v>臺灣中小企業銀行</v>
       </c>
     </row>
@@ -5787,7 +6244,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A73,AI應用場景!B:B,B73)</f>
         <v>1</v>
       </c>
-      <c r="G73" s="22" t="str">
+      <c r="G73" s="16" t="str">
         <v>臺灣中小企銀</v>
       </c>
     </row>
@@ -5805,7 +6262,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A74,AI應用場景!B:B,B74)</f>
         <v>2</v>
       </c>
-      <c r="G74" s="22" t="str">
+      <c r="G74" s="16" t="str">
         <v>臺灣金控</v>
       </c>
     </row>
@@ -5823,7 +6280,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A75,AI應用場景!B:B,B75)</f>
         <v>1</v>
       </c>
-      <c r="G75" s="22" t="str">
+      <c r="G75" s="16" t="str">
         <v>臺灣銀行</v>
       </c>
     </row>
@@ -5841,7 +6298,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A76,AI應用場景!B:B,B76)</f>
         <v>1</v>
       </c>
-      <c r="G76" s="22" t="str">
+      <c r="G76" s="16" t="str">
         <v>遠傳保險代理人股份有限公司</v>
       </c>
     </row>
@@ -5859,7 +6316,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A77,AI應用場景!B:B,B77)</f>
         <v>1</v>
       </c>
-      <c r="G77" s="22" t="str">
+      <c r="G77" s="16" t="str">
         <v>德信證券</v>
       </c>
     </row>
@@ -5877,7 +6334,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A78,AI應用場景!B:B,B78)</f>
         <v>1</v>
       </c>
-      <c r="G78" s="22" t="str">
+      <c r="G78" s="16" t="str">
         <v>摩根投信</v>
       </c>
     </row>
@@ -5895,7 +6352,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A79,AI應用場景!B:B,B79)</f>
         <v>1</v>
       </c>
-      <c r="G79" s="22" t="str">
+      <c r="G79" s="16" t="str">
         <v>樂天銀行</v>
       </c>
     </row>
@@ -5913,7 +6370,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A80,AI應用場景!B:B,B80)</f>
         <v>1</v>
       </c>
-      <c r="G80" s="22" t="str">
+      <c r="G80" s="16" t="str">
         <v>錠嵂保險經紀人股份有限公司</v>
       </c>
     </row>
@@ -5931,7 +6388,7 @@
         <f>COUNTIFS(AI應用場景!A:A,A81,AI應用場景!B:B,B81)</f>
         <v>1</v>
       </c>
-      <c r="G81" s="22" t="str">
+      <c r="G81" s="16" t="str">
         <v>聯卡中心</v>
       </c>
     </row>
@@ -5949,7 +6406,7 @@
         <f>COUNTIF(AI應用場景!B:B, B82)</f>
         <v>2</v>
       </c>
-      <c r="G82" s="22" t="str">
+      <c r="G82" s="16" t="str">
         <v>聯博投信</v>
       </c>
     </row>
@@ -5967,12 +6424,12 @@
         <f>COUNTIF(AI應用場景!B:B, B83)</f>
         <v>1</v>
       </c>
-      <c r="G83" s="22" t="str">
+      <c r="G83" s="16" t="str">
         <v>證券交易所</v>
       </c>
     </row>
     <row r="84" spans="1:7">
-      <c r="G84" s="22"/>
+      <c r="G84" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -5999,26 +6456,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32.1" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="F1" s="25" t="s">
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="F1" s="27" t="s">
         <v>291</v>
       </c>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
     </row>
     <row r="2" spans="1:9" ht="72" customHeight="1">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
       <c r="F2" s="28" t="s">
         <v>342</v>
       </c>
@@ -6031,10 +6488,10 @@
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="9" t="s">
@@ -6049,16 +6506,16 @@
       <c r="D4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="34" t="s">
+      <c r="F4" s="25" t="s">
         <v>292</v>
       </c>
-      <c r="G4" s="34" t="s">
+      <c r="G4" s="25" t="s">
         <v>339</v>
       </c>
-      <c r="H4" s="34" t="s">
+      <c r="H4" s="25" t="s">
         <v>289</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="I4" s="19" t="s">
         <v>5</v>
       </c>
     </row>
@@ -6076,14 +6533,14 @@
         <f>COUNTIF(AI應用場景!E:E,A5)</f>
         <v>10</v>
       </c>
-      <c r="F5" s="32" t="s">
+      <c r="F5" s="23" t="s">
         <v>293</v>
       </c>
-      <c r="G5" s="32"/>
-      <c r="H5" s="32" t="s">
+      <c r="G5" s="23"/>
+      <c r="H5" s="23" t="s">
         <v>294</v>
       </c>
-      <c r="I5" s="29">
+      <c r="I5" s="21">
         <f>COUNTIF(金融業AI場景明細[所屬金控],H5)</f>
         <v>5</v>
       </c>
@@ -6102,14 +6559,14 @@
         <f>COUNTIF(AI應用場景!E:E,A6)</f>
         <v>10</v>
       </c>
-      <c r="F6" s="32" t="s">
+      <c r="F6" s="23" t="s">
         <v>295</v>
       </c>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32" t="s">
+      <c r="G6" s="23"/>
+      <c r="H6" s="23" t="s">
         <v>296</v>
       </c>
-      <c r="I6" s="29">
+      <c r="I6" s="21">
         <f>COUNTIF(金融業AI場景明細[所屬金控],H6)</f>
         <v>18</v>
       </c>
@@ -6128,16 +6585,16 @@
         <f>COUNTIF(AI應用場景!E:E,A7)</f>
         <v>32</v>
       </c>
-      <c r="F7" s="32" t="s">
+      <c r="F7" s="23" t="s">
         <v>297</v>
       </c>
-      <c r="G7" s="32" t="s">
+      <c r="G7" s="23" t="s">
         <v>298</v>
       </c>
-      <c r="H7" s="32" t="s">
+      <c r="H7" s="23" t="s">
         <v>299</v>
       </c>
-      <c r="I7" s="29">
+      <c r="I7" s="21">
         <f>COUNTIF(金融業AI場景明細[所屬金控],H7)</f>
         <v>9</v>
       </c>
@@ -6156,16 +6613,16 @@
         <f>COUNTIF(AI應用場景!E:E,A8)</f>
         <v>3</v>
       </c>
-      <c r="F8" s="32" t="s">
+      <c r="F8" s="23" t="s">
         <v>300</v>
       </c>
-      <c r="G8" s="32" t="s">
+      <c r="G8" s="23" t="s">
         <v>324</v>
       </c>
-      <c r="H8" s="32" t="s">
+      <c r="H8" s="23" t="s">
         <v>301</v>
       </c>
-      <c r="I8" s="29">
+      <c r="I8" s="21">
         <f>COUNTIF(金融業AI場景明細[所屬金控],H8)</f>
         <v>6</v>
       </c>
@@ -6184,16 +6641,16 @@
         <f>COUNTIF(AI應用場景!E:E,A9)</f>
         <v>14</v>
       </c>
-      <c r="F9" s="32" t="s">
+      <c r="F9" s="23" t="s">
         <v>302</v>
       </c>
-      <c r="G9" s="32" t="s">
+      <c r="G9" s="23" t="s">
         <v>303</v>
       </c>
-      <c r="H9" s="32" t="s">
+      <c r="H9" s="23" t="s">
         <v>304</v>
       </c>
-      <c r="I9" s="29">
+      <c r="I9" s="21">
         <f>COUNTIF(金融業AI場景明細[所屬金控],H9)</f>
         <v>3</v>
       </c>
@@ -6212,14 +6669,14 @@
         <f>COUNTIF(AI應用場景!E:E,A10)</f>
         <v>9</v>
       </c>
-      <c r="F10" s="32" t="s">
+      <c r="F10" s="23" t="s">
         <v>305</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32" t="s">
+      <c r="G10" s="23"/>
+      <c r="H10" s="23" t="s">
         <v>306</v>
       </c>
-      <c r="I10" s="29">
+      <c r="I10" s="21">
         <f>COUNTIF(金融業AI場景明細[所屬金控],H10)</f>
         <v>2</v>
       </c>
@@ -6238,16 +6695,16 @@
         <f>COUNTIF(AI應用場景!E:E,A11)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="32" t="s">
+      <c r="F11" s="23" t="s">
         <v>307</v>
       </c>
-      <c r="G11" s="32" t="s">
+      <c r="G11" s="23" t="s">
         <v>308</v>
       </c>
-      <c r="H11" s="32" t="s">
+      <c r="H11" s="23" t="s">
         <v>309</v>
       </c>
-      <c r="I11" s="29">
+      <c r="I11" s="21">
         <f>COUNTIF(金融業AI場景明細[所屬金控],H11)</f>
         <v>9</v>
       </c>
@@ -6266,14 +6723,14 @@
         <f>COUNTIF(AI應用場景!E:E,A12)</f>
         <v>2</v>
       </c>
-      <c r="F12" s="32" t="s">
+      <c r="F12" s="23" t="s">
         <v>310</v>
       </c>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32" t="s">
+      <c r="G12" s="23"/>
+      <c r="H12" s="23" t="s">
         <v>311</v>
       </c>
-      <c r="I12" s="29">
+      <c r="I12" s="21">
         <f>COUNTIF(金融業AI場景明細[所屬金控],H12)</f>
         <v>3</v>
       </c>
@@ -6292,14 +6749,14 @@
         <f>COUNTIF(AI應用場景!E:E,A13)</f>
         <v>12</v>
       </c>
-      <c r="F13" s="32" t="s">
+      <c r="F13" s="23" t="s">
         <v>312</v>
       </c>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32" t="s">
+      <c r="G13" s="23"/>
+      <c r="H13" s="23" t="s">
         <v>313</v>
       </c>
-      <c r="I13" s="29">
+      <c r="I13" s="21">
         <f>COUNTIF(金融業AI場景明細[所屬金控],H13)</f>
         <v>2</v>
       </c>
@@ -6318,14 +6775,14 @@
         <f>COUNTIF(AI應用場景!E:E,A14)</f>
         <v>5</v>
       </c>
-      <c r="F14" s="32" t="s">
+      <c r="F14" s="23" t="s">
         <v>314</v>
       </c>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32" t="s">
+      <c r="G14" s="23"/>
+      <c r="H14" s="23" t="s">
         <v>315</v>
       </c>
-      <c r="I14" s="29">
+      <c r="I14" s="21">
         <f>COUNTIF(金融業AI場景明細[所屬金控],H14)</f>
         <v>0</v>
       </c>
@@ -6344,14 +6801,14 @@
         <f>COUNTIF(AI應用場景!E:E,A15)</f>
         <v>6</v>
       </c>
-      <c r="F15" s="32" t="s">
+      <c r="F15" s="23" t="s">
         <v>316</v>
       </c>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32" t="s">
+      <c r="G15" s="23"/>
+      <c r="H15" s="23" t="s">
         <v>317</v>
       </c>
-      <c r="I15" s="29">
+      <c r="I15" s="21">
         <f>COUNTIF(金融業AI場景明細[所屬金控],H15)</f>
         <v>7</v>
       </c>
@@ -6370,14 +6827,14 @@
         <f>COUNTIF(AI應用場景!E:E,A16)</f>
         <v>6</v>
       </c>
-      <c r="F16" s="32" t="s">
+      <c r="F16" s="23" t="s">
         <v>318</v>
       </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32" t="s">
+      <c r="G16" s="23"/>
+      <c r="H16" s="23" t="s">
         <v>319</v>
       </c>
-      <c r="I16" s="29">
+      <c r="I16" s="21">
         <f>COUNTIF(金融業AI場景明細[所屬金控],H16)</f>
         <v>0</v>
       </c>
@@ -6396,14 +6853,14 @@
         <f>COUNTIF(AI應用場景!E:E,A17)</f>
         <v>3</v>
       </c>
-      <c r="F17" s="32" t="s">
+      <c r="F17" s="23" t="s">
         <v>320</v>
       </c>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32" t="s">
+      <c r="G17" s="23"/>
+      <c r="H17" s="23" t="s">
         <v>321</v>
       </c>
-      <c r="I17" s="29">
+      <c r="I17" s="21">
         <f>COUNTIF(金融業AI場景明細[所屬金控],H17)</f>
         <v>0</v>
       </c>
@@ -6422,38 +6879,38 @@
         <f>COUNTIF(AI應用場景!E:E,A18)</f>
         <v>31</v>
       </c>
-      <c r="F18" s="32" t="s">
+      <c r="F18" s="23" t="s">
         <v>340</v>
       </c>
-      <c r="G18" s="32" t="s">
+      <c r="G18" s="23" t="s">
         <v>341</v>
       </c>
-      <c r="H18" s="32" t="s">
+      <c r="H18" s="23" t="s">
         <v>336</v>
       </c>
-      <c r="I18" s="29">
+      <c r="I18" s="21">
         <f>COUNTIF(金融業AI場景明細[所屬金控],H18)</f>
         <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="31"/>
       <c r="D19" s="7">
         <f>SUM(D5:D18)</f>
         <v>143</v>
       </c>
-      <c r="F19" s="35" t="s">
+      <c r="F19" s="29" t="s">
         <v>323</v>
       </c>
-      <c r="G19" s="35"/>
-      <c r="H19" s="32" t="s">
+      <c r="G19" s="29"/>
+      <c r="H19" s="23" t="s">
         <v>322</v>
       </c>
-      <c r="I19" s="29">
+      <c r="I19" s="21">
         <f>COUNTIF(金融業AI場景明細[所屬金控],H19)</f>
         <v>77</v>
       </c>
@@ -6463,92 +6920,92 @@
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
-      <c r="F20" s="36" t="s">
+      <c r="F20" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="G20" s="36"/>
-      <c r="H20" s="36"/>
-      <c r="I20" s="30">
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="22">
         <f>SUM(I5:I19)</f>
         <v>143</v>
       </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="16" t="str">
+      <c r="A22" s="30" t="str">
         <f>"整理單位：共 80 個業者／周邊單位、"&amp;D19&amp;" 筆場景；保留原文業別及出現順序，不依業者名稱重新推定監理業別。"</f>
         <v>整理單位：共 80 個業者／周邊單位、143 筆場景；保留原文業別及出現順序，不依業者名稱重新推定監理業別。</v>
       </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
     </row>
     <row r="23" spans="1:9" ht="189.95" customHeight="1">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
+      <c r="B23" s="31"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
     </row>
     <row r="24" spans="1:9" ht="56.1" customHeight="1">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
+      <c r="B24" s="31"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
     </row>
     <row r="25" spans="1:9" ht="36" customHeight="1">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
+      <c r="B25" s="31"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
+      <c r="B26" s="31"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="16" t="s">
+      <c r="A27" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
+      <c r="B27" s="31"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="16" t="s">
+      <c r="A28" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
+      <c r="B28" s="31"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="16" t="s">
+      <c r="A29" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
+      <c r="B29" s="31"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="16">

--- a/金融業AI場景應用.xlsx
+++ b/金融業AI場景應用.xlsx
@@ -563,8 +563,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="金融業AI場景明細" displayName="金融業AI場景明細" ref="A1:F178" headerRowCount="1" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:F178"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="金融業AI場景明細" displayName="金融業AI場景明細" ref="A1:F186" headerRowCount="1" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:F186"/>
   <tableColumns count="6">
     <tableColumn id="1" name="業別" dataDxfId="10"/>
     <tableColumn id="2" name="業者" dataDxfId="9"/>
@@ -913,7 +913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F178"/>
+  <dimension ref="A1:F186"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="11.1640625" bestFit="1" customWidth="1" style="28" min="1" max="1"/>
@@ -6266,18 +6266,258 @@
         <v>46322</v>
       </c>
     </row>
+    <row r="179">
+      <c r="A179" s="3" t="inlineStr">
+        <is>
+          <t>證券期貨業</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>凱基證券</t>
+        </is>
+      </c>
+      <c r="C179" s="20" t="inlineStr">
+        <is>
+          <t>凱基金</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>打造「AI 投研智慧釀酒廠」，採用 Data × Skill × Cowork 架構整合資料與專家知識，由生成式 AI 自動執行研究資料蒐集、分析比對與報告產製。</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
+        <is>
+          <t>生成式AI</t>
+        </is>
+      </c>
+      <c r="F179" s="37" t="n">
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>保險業</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>凱基人壽</t>
+        </is>
+      </c>
+      <c r="C180" s="20" t="inlineStr">
+        <is>
+          <t>凱基金</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>自主研發「IDEA 智慧幕僚平台」，結合生成式 AI、OCR 與大數據分析落地核保、理賠、人資與風控，提供職務說明生成、會議摘要與智慧文件判讀。</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="inlineStr">
+        <is>
+          <t>生成式AI</t>
+        </is>
+      </c>
+      <c r="F180" s="37" t="n">
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t>保險業</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>國泰人壽</t>
+        </is>
+      </c>
+      <c r="C181" s="20" t="inlineStr">
+        <is>
+          <t>國泰金</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>以「LifeLink」串聯國泰人壽 App 與新業務平台（NAP），推出「AI 全能助手」與「AI 保單辨識」（辨識率達 95%），拍照或上傳即可自動建檔並產出保單健檢。</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="F181" s="37" t="n">
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>保險業</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>國泰產險</t>
+        </is>
+      </c>
+      <c r="C182" s="20" t="inlineStr">
+        <is>
+          <t>國泰金</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>將 AI 深度導入理賠核心流程加速單據審核與智慧估損，使估損時間效率大幅提升 83%、每年節省逾 1,000 小時工時，保戶平均提前 7 天獲得理賠。</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="inlineStr">
+        <is>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="F182" s="37" t="n">
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="inlineStr">
+        <is>
+          <t>銀行業</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>台新銀行</t>
+        </is>
+      </c>
+      <c r="C183" s="20" t="inlineStr">
+        <is>
+          <t>台新新光金</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>推出「LUNA」AI 個人信貸決策模型，採多任務深度學習（MTL）結合作業研究演算法同步優化核准率、額度與利率，帶動月撥款成長近三成並節省 90% 維運人力。</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="inlineStr">
+        <is>
+          <t>模型訓練</t>
+        </is>
+      </c>
+      <c r="F183" s="37" t="n">
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="inlineStr">
+        <is>
+          <t>銀行業</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>中國信託銀行</t>
+        </is>
+      </c>
+      <c r="C184" s="20" t="inlineStr">
+        <is>
+          <t>中信金</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>打造小微企業「一站式智慧融資平台（SWIP）」，結合 AI 自動化查驗、數位徵審與遠距對保重構申貸流程，使申貸審查時效大幅縮短逾 70%。</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="inlineStr">
+        <is>
+          <t>RPA</t>
+        </is>
+      </c>
+      <c r="F184" s="37" t="n">
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>銀行業</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>台北富邦銀行</t>
+        </is>
+      </c>
+      <c r="C185" s="20" t="inlineStr">
+        <is>
+          <t>富邦金</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>建置「制度化即時市場風險治理與自主評價智能風控整合平台」，結合 AI 智慧監控、自主評價模型與雲端 GPU 平行運算，使衍生性商品評價與風險計算時間縮短 90%。</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="inlineStr">
+        <is>
+          <t>模型訓練</t>
+        </is>
+      </c>
+      <c r="F185" s="37" t="n">
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="inlineStr">
+        <is>
+          <t>銀行業</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>永豐銀行</t>
+        </is>
+      </c>
+      <c r="C186" s="20" t="inlineStr">
+        <is>
+          <t>永豐金</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>於信貸與信用卡徵審導入「所得代理模型」，運用 AI 與大數據分析逾 470 項帳戶金流與行為參數，協助無固定薪資證明之多元職業族群完成信用評估。</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="inlineStr">
+        <is>
+          <t>模型訓練</t>
+        </is>
+      </c>
+      <c r="F186" s="37" t="n">
+        <v>46323</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="E2:E178" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="請選擇有效類別" error="請使用下拉選單中的類別，分類項目請參閱「分類說明」。" type="list">
+    <dataValidation sqref="E2:E186" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="請選擇有效類別" error="請使用下拉選單中的類別，分類項目請參閱「分類說明」。" type="list">
       <formula1>類別選項</formula1>
     </dataValidation>
-    <dataValidation sqref="A2:A178" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="A2:A186" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>業別選項</formula1>
     </dataValidation>
-    <dataValidation sqref="B2:B178" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B186" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>業者選項</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C178" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C186" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>所屬金控選項</formula1>
     </dataValidation>
   </dataValidations>

--- a/金融業AI場景應用.xlsx
+++ b/金融業AI場景應用.xlsx
@@ -563,8 +563,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="金融業AI場景明細" displayName="金融業AI場景明細" ref="A1:F186" headerRowCount="1" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:F186"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="金融業AI場景明細" displayName="金融業AI場景明細" ref="A1:F195" headerRowCount="1" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:F195"/>
   <tableColumns count="6">
     <tableColumn id="1" name="業別" dataDxfId="10"/>
     <tableColumn id="2" name="業者" dataDxfId="9"/>
@@ -578,8 +578,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="業者來源索引" displayName="業者來源索引" ref="A1:D91" headerRowCount="1" totalsRowShown="0" headerRowDxfId="4">
-  <autoFilter ref="A1:D91"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="業者來源索引" displayName="業者來源索引" ref="A1:D93" headerRowCount="1" totalsRowShown="0" headerRowDxfId="4">
+  <autoFilter ref="A1:D93"/>
   <tableColumns count="4">
     <tableColumn id="1" name="業別" dataDxfId="3"/>
     <tableColumn id="2" name="業者" dataDxfId="2"/>
@@ -913,7 +913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F186"/>
+  <dimension ref="A1:F195"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="11.1640625" bestFit="1" customWidth="1" style="28" min="1" max="1"/>
@@ -6506,18 +6506,288 @@
         <v>46323</v>
       </c>
     </row>
+    <row r="187">
+      <c r="A187" s="3" t="inlineStr">
+        <is>
+          <t>銀行業</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>國泰世華銀行</t>
+        </is>
+      </c>
+      <c r="C187" s="20" t="inlineStr">
+        <is>
+          <t>國泰金</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>打造「理專 AI 助手」聚焦高頻電訪流程，透過生成式 AI 自動整理非結構化通話內容，彙整客戶溝通重點、需求線索與互動訊號，獲首屆 AI 智能實踐典範獎。</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="inlineStr">
+        <is>
+          <t>語音質檢/應用</t>
+        </is>
+      </c>
+      <c r="F187" s="37" t="n">
+        <v>46324</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="inlineStr">
+        <is>
+          <t>證券期貨業</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>國泰證券</t>
+        </is>
+      </c>
+      <c r="C188" s="20" t="inlineStr">
+        <is>
+          <t>國泰金</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>啟動「AI 驅動轉型計畫」，結合生成式 AI 與 NLP 升級「AI 庫存管家」與「AI 台股投資日報」，於盤中即時偵測持股異常波動並推播千人千面個人化新聞摘要。</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="inlineStr">
+        <is>
+          <t>生成式AI</t>
+        </is>
+      </c>
+      <c r="F188" s="37" t="n">
+        <v>46324</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="inlineStr">
+        <is>
+          <t>銀行業</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
+        <is>
+          <t>玉山銀行</t>
+        </is>
+      </c>
+      <c r="C189" s="20" t="inlineStr">
+        <is>
+          <t>玉山金</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t>於分行部署結合 Vertex AI Search 與 RAG 技術之行員專用 AI 助手「金秘書」加速法規與流程檢索，並於零售端推出「投資 i-chat」與「AI 房貸顧問」，獲亞洲銀行家台灣最佳零售銀行生成式 AI 應用獎。</t>
+        </is>
+      </c>
+      <c r="E189" s="3" t="inlineStr">
+        <is>
+          <t>RAG/KM</t>
+        </is>
+      </c>
+      <c r="F189" s="37" t="n">
+        <v>46324</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="3" t="inlineStr">
+        <is>
+          <t>銀行業</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>玉山銀行</t>
+        </is>
+      </c>
+      <c r="C190" s="20" t="inlineStr">
+        <is>
+          <t>玉山金</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>建置「電話客服中心語意資料庫與口語化智能語音導航系統」，結合 NLU、語音轉文字與 100% 通話合規監控，讓顧客以自然口語取代按鍵選單，操作時間縮短 60%。</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="inlineStr">
+        <is>
+          <t>語音質檢/應用</t>
+        </is>
+      </c>
+      <c r="F190" s="37" t="n">
+        <v>46324</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="inlineStr">
+        <is>
+          <t>證券期貨業</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>富邦投顧</t>
+        </is>
+      </c>
+      <c r="C191" s="20" t="inlineStr">
+        <is>
+          <t>富邦金</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>推出「AI × 投研報告 × 影音內容」會員服務優化方案，運用生成式 AI 將純文字研究報告自動轉化為短影音、Podcast、AI 主播播報與視覺化圖卡。</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="inlineStr">
+        <is>
+          <t>生成式AI</t>
+        </is>
+      </c>
+      <c r="F191" s="37" t="n">
+        <v>46324</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="inlineStr">
+        <is>
+          <t>保險業</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>新光人壽</t>
+        </is>
+      </c>
+      <c r="C192" s="20" t="inlineStr">
+        <is>
+          <t>台新新光金</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>攜手 AWS 導入「跨機構保險理賠風險聯防聯合學習（Federated Learning）與合成資料技術」訓練 AI 理賠防詐模型，並引進新一代「AI 智慧線上理賠系統」。</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="inlineStr">
+        <is>
+          <t>模型訓練</t>
+        </is>
+      </c>
+      <c r="F192" s="37" t="n">
+        <v>46324</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="3" t="inlineStr">
+        <is>
+          <t>銀行業</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>凱基銀行</t>
+        </is>
+      </c>
+      <c r="C193" s="20" t="inlineStr">
+        <is>
+          <t>凱基金</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>建構「AI RADAR 智能雷達防詐網」，結合 AI 大數據與跨機構聯邦式學習（Federated Learning）貫穿五大防詐面向，大幅提升警示帳戶辨識精確率並降低誤判率。</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="inlineStr">
+        <is>
+          <t>阻詐</t>
+        </is>
+      </c>
+      <c r="F193" s="37" t="n">
+        <v>46324</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="inlineStr">
+        <is>
+          <t>證券期貨業</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>中國信託證券</t>
+        </is>
+      </c>
+      <c r="C194" s="20" t="inlineStr">
+        <is>
+          <t>中信金</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>於「中信亮點 App」串聯 AI 與大數據分析，推出「你可能會喜歡」個人化推薦引擎、ETF 比較器與智能投組服務。</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="F194" s="37" t="n">
+        <v>46324</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="3" t="inlineStr">
+        <is>
+          <t>銀行業</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>合作金庫銀行</t>
+        </is>
+      </c>
+      <c r="C195" s="20" t="inlineStr">
+        <is>
+          <t>合庫金</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>透過跨部門創新實驗室「CoLAB」舉辦「合力智造 CO X Copilot」黑客松推動 Microsoft Copilot 金融實務與知識管理應用，並取得 BSI 全球首張「AI 信賴標誌（AI Mark of Trust）」。</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>M365 Copilot</t>
+        </is>
+      </c>
+      <c r="F195" s="37" t="n">
+        <v>46324</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="E2:E186" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="請選擇有效類別" error="請使用下拉選單中的類別，分類項目請參閱「分類說明」。" type="list">
+    <dataValidation sqref="E2:E195" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="請選擇有效類別" error="請使用下拉選單中的類別，分類項目請參閱「分類說明」。" type="list">
       <formula1>類別選項</formula1>
     </dataValidation>
-    <dataValidation sqref="A2:A186" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="A2:A195" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>業別選項</formula1>
     </dataValidation>
-    <dataValidation sqref="B2:B186" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B195" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>業者選項</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C186" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C195" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>所屬金控選項</formula1>
     </dataValidation>
   </dataValidations>
@@ -6534,7 +6804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H93"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="14.33203125" customWidth="1" style="28" min="1" max="1"/>
@@ -8814,6 +9084,48 @@
       </c>
       <c r="D91" s="5">
         <f>COUNTIFS(AI應用場景!A:A,A91,AI應用場景!B:B,B91)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="30" t="inlineStr">
+        <is>
+          <t>證券期貨業</t>
+        </is>
+      </c>
+      <c r="B92" s="30" t="inlineStr">
+        <is>
+          <t>富邦投顧</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>最新蒐集</t>
+        </is>
+      </c>
+      <c r="D92" s="5">
+        <f>COUNTIFS(AI應用場景!A:A,A92,AI應用場景!B:B,B92)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="30" t="inlineStr">
+        <is>
+          <t>證券期貨業</t>
+        </is>
+      </c>
+      <c r="B93" s="30" t="inlineStr">
+        <is>
+          <t>中國信託證券</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>最新蒐集</t>
+        </is>
+      </c>
+      <c r="D93" s="5">
+        <f>COUNTIFS(AI應用場景!A:A,A93,AI應用場景!B:B,B93)</f>
         <v/>
       </c>
     </row>

--- a/金融業AI場景應用.xlsx
+++ b/金融業AI場景應用.xlsx
@@ -563,8 +563,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="金融業AI場景明細" displayName="金融業AI場景明細" ref="A1:F195" headerRowCount="1" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:F195"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="金融業AI場景明細" displayName="金融業AI場景明細" ref="A1:F205" headerRowCount="1" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:F205"/>
   <tableColumns count="6">
     <tableColumn id="1" name="業別" dataDxfId="10"/>
     <tableColumn id="2" name="業者" dataDxfId="9"/>
@@ -578,8 +578,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="業者來源索引" displayName="業者來源索引" ref="A1:D93" headerRowCount="1" totalsRowShown="0" headerRowDxfId="4">
-  <autoFilter ref="A1:D93"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="業者來源索引" displayName="業者來源索引" ref="A1:D94" headerRowCount="1" totalsRowShown="0" headerRowDxfId="4">
+  <autoFilter ref="A1:D94"/>
   <tableColumns count="4">
     <tableColumn id="1" name="業別" dataDxfId="3"/>
     <tableColumn id="2" name="業者" dataDxfId="2"/>
@@ -913,7 +913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F195"/>
+  <dimension ref="A1:F205"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="11.1640625" bestFit="1" customWidth="1" style="28" min="1" max="1"/>
@@ -6776,18 +6776,318 @@
         <v>46324</v>
       </c>
     </row>
+    <row r="196">
+      <c r="A196" s="3" t="inlineStr">
+        <is>
+          <t>保險業</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>富邦人壽</t>
+        </is>
+      </c>
+      <c r="C196" s="20" t="inlineStr">
+        <is>
+          <t>富邦金</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>打造「核保智能助理」結合生成式 AI 與個資遮罩工具自動摘要百頁中英文病歷，使體況審查時間由 40 分鐘縮短至 15 分鐘（效率提升 60%），並以 AI 輔助理賠條款今昔比對，獲 AI 智能實踐典範獎。</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="inlineStr">
+        <is>
+          <t>生成式AI</t>
+        </is>
+      </c>
+      <c r="F196" s="37" t="n">
+        <v>46325</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="inlineStr">
+        <is>
+          <t>保險業</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>富邦產險</t>
+        </is>
+      </c>
+      <c r="C197" s="20" t="inlineStr">
+        <is>
+          <t>富邦金</t>
+        </is>
+      </c>
+      <c r="D197" s="3" t="inlineStr">
+        <is>
+          <t>推出結合 AI 人臉辨識、數位身分驗證與線上簽署之「FacePass 極速保」零摩擦投保服務，並整合 GIS 與 AI 風險模型打造業務端「行動智能地圖」。</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="inlineStr">
+        <is>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="F197" s="37" t="n">
+        <v>46325</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="3" t="inlineStr">
+        <is>
+          <t>證券期貨業</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>玉山證券</t>
+        </is>
+      </c>
+      <c r="C198" s="20" t="inlineStr">
+        <is>
+          <t>玉山金</t>
+        </is>
+      </c>
+      <c r="D198" s="3" t="inlineStr">
+        <is>
+          <t>於全新官方 App 打造「庫存專區 × AI 智慧投資助手」，結合基本面、技術面與籌碼面指標提供「AI 分析月趨勢評分」、多維度庫存健診與投組風險集中度評估。</t>
+        </is>
+      </c>
+      <c r="E198" s="3" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="F198" s="37" t="n">
+        <v>46325</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="3" t="inlineStr">
+        <is>
+          <t>證券期貨業</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="inlineStr">
+        <is>
+          <t>玉山證券</t>
+        </is>
+      </c>
+      <c r="C199" s="20" t="inlineStr">
+        <is>
+          <t>玉山金</t>
+        </is>
+      </c>
+      <c r="D199" s="3" t="inlineStr">
+        <is>
+          <t>協同玉山金控與玉山投信舉辦「AI CUP 2026 玉山人工智慧公開挑戰賽」，推動「Agent 基金經理人」運用大型語言模型自主執行台股 ETF 選股、動態資產配置與每日交易報告產出。</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="inlineStr">
+        <is>
+          <t>AI Agent</t>
+        </is>
+      </c>
+      <c r="F199" s="37" t="n">
+        <v>46325</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="inlineStr">
+        <is>
+          <t>保險業</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>凱基人壽</t>
+        </is>
+      </c>
+      <c r="C200" s="20" t="inlineStr">
+        <is>
+          <t>凱基金</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>建置營運知識引擎與角色化內勤智能助理群（核保寶、查理、保服寶），整合上千份作業規範輔助核保、理賠與保全即時檢索判斷，獲 AI 智能實踐典範獎。</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="inlineStr">
+        <is>
+          <t>RAG/KM</t>
+        </is>
+      </c>
+      <c r="F200" s="37" t="n">
+        <v>46325</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="3" t="inlineStr">
+        <is>
+          <t>保險業</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>凱基人壽</t>
+        </is>
+      </c>
+      <c r="C201" s="20" t="inlineStr">
+        <is>
+          <t>凱基金</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>導入結合 AI 與光學字元辨識（OCR）之「醫療文件智慧判讀系統」，自動辨識複雜病歷與診斷證明書並萃取關鍵醫療資訊，縮短人工審閱時間並降低誤判率。</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="F201" s="37" t="n">
+        <v>46325</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="3" t="inlineStr">
+        <is>
+          <t>證券期貨業</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t>元大期貨</t>
+        </is>
+      </c>
+      <c r="C202" s="20" t="inlineStr">
+        <is>
+          <t>元大金</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>將 AI 與智能化工具深度導入期貨及槓桿交易營運、一站式智慧開戶審查、智能客服、異常交易風險預警與防詐監測，榮獲首屆 AI 智能實踐典範獎金質獎。</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="inlineStr">
+        <is>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="F202" s="37" t="n">
+        <v>46325</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="3" t="inlineStr">
+        <is>
+          <t>保險業</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="inlineStr">
+        <is>
+          <t>元大人壽</t>
+        </is>
+      </c>
+      <c r="C203" s="20" t="inlineStr">
+        <is>
+          <t>元大金</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>於內部稽核作業導入「JCAATs AI 智能稽核軟體」，運用大數據與機器學習技術強化內控查核與異常風險偵測。</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="inlineStr">
+        <is>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="F203" s="37" t="n">
+        <v>46325</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="inlineStr">
+        <is>
+          <t>銀行業</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>第一銀行</t>
+        </is>
+      </c>
+      <c r="C204" s="20" t="inlineStr">
+        <is>
+          <t>第一金</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>建置全行「知識管理 AI 智能詢答平台」，運用 LLM 與檢索增強生成（RAG）技術整合跨部門規章手冊，支援即問即答與相似提問自動推演。</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="inlineStr">
+        <is>
+          <t>RAG/KM</t>
+        </is>
+      </c>
+      <c r="F204" s="37" t="n">
+        <v>46325</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="inlineStr">
+        <is>
+          <t>銀行業</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>臺灣中小企銀</t>
+        </is>
+      </c>
+      <c r="C205" s="20" t="inlineStr">
+        <is>
+          <t>未歸類</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>導入「AI 模型投資阻詐示警服務」結合 WISDOM 智慧安全防禦機制，動態偵測異常投資金流與詐騙交易特徵，榮獲數位金融獎防詐組金質獎。</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="inlineStr">
+        <is>
+          <t>阻詐</t>
+        </is>
+      </c>
+      <c r="F205" s="37" t="n">
+        <v>46325</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="E2:E195" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="請選擇有效類別" error="請使用下拉選單中的類別，分類項目請參閱「分類說明」。" type="list">
+    <dataValidation sqref="E2:E205" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="請選擇有效類別" error="請使用下拉選單中的類別，分類項目請參閱「分類說明」。" type="list">
       <formula1>類別選項</formula1>
     </dataValidation>
-    <dataValidation sqref="A2:A195" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="A2:A205" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>業別選項</formula1>
     </dataValidation>
-    <dataValidation sqref="B2:B195" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B205" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>業者選項</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C195" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C205" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>所屬金控選項</formula1>
     </dataValidation>
   </dataValidations>
@@ -6804,7 +7104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H93"/>
+  <dimension ref="A1:H94"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="14.33203125" customWidth="1" style="28" min="1" max="1"/>
@@ -9126,6 +9426,27 @@
       </c>
       <c r="D93" s="5">
         <f>COUNTIFS(AI應用場景!A:A,A93,AI應用場景!B:B,B93)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="30" t="inlineStr">
+        <is>
+          <t>證券期貨業</t>
+        </is>
+      </c>
+      <c r="B94" s="30" t="inlineStr">
+        <is>
+          <t>元大期貨</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>最新蒐集</t>
+        </is>
+      </c>
+      <c r="D94" s="5">
+        <f>COUNTIFS(AI應用場景!A:A,A94,AI應用場景!B:B,B94)</f>
         <v/>
       </c>
     </row>
